--- a/M1/Gantt.xlsx
+++ b/M1/Gantt.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>Projekt kezdete:</t>
   </si>
@@ -142,31 +142,49 @@
     <t xml:space="preserve">     8.2.1 Use Case diagram</t>
   </si>
   <si>
+    <t>Kovács Bence</t>
+  </si>
+  <si>
     <t xml:space="preserve">     8.2.2 Class Diagram</t>
+  </si>
+  <si>
+    <t>Fodor Döme</t>
   </si>
   <si>
     <t xml:space="preserve">     8.2.3 Sequence diagram</t>
   </si>
   <si>
+    <t>Madai Zsuzsannna J.</t>
+  </si>
+  <si>
     <t xml:space="preserve">     8.2.4 Egyed-kapcsolat diagram adatbázishoz</t>
   </si>
   <si>
-    <t>Petra</t>
+    <t>Sötét Petra</t>
   </si>
   <si>
     <t xml:space="preserve">     8.2.5 Package diagram</t>
   </si>
   <si>
+    <t>Zsemberi Izabella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     8.2.6 Weboldal design elkészítése Figmában</t>
+  </si>
+  <si>
+    <t>Kromek Dániel B.</t>
+  </si>
+  <si>
     <t xml:space="preserve">     8.2.7 Bemutató elkészítése</t>
+  </si>
+  <si>
+    <t>Nagy Sz. Kamilla</t>
   </si>
   <si>
     <t>3. Mérföldkő (Commit - 6, Issue - 2)</t>
   </si>
   <si>
     <t xml:space="preserve">     8.3.1 Projekt létrehozása Angular-ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Iza</t>
   </si>
   <si>
     <t xml:space="preserve">     8.3.2 Felhasználók kezelése (UD)</t>
@@ -182,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">     8.3.6 Oldalakhoz szükséges adatok létrehozása adatbázisban</t>
+  </si>
+  <si>
+    <t>Madai Zsuzsanna J.</t>
   </si>
   <si>
     <t xml:space="preserve">     8.3.7 Hirdetések kezelése (C)</t>
@@ -256,37 +277,16 @@
     <t xml:space="preserve">     8.4.11 A prototípus kitelepítésének frissítése</t>
   </si>
   <si>
-    <t>Madai Zsuzsannna J.</t>
-  </si>
-  <si>
     <t>FrontEnd &amp; adatb</t>
-  </si>
-  <si>
-    <t>Kromek Dániel B.</t>
   </si>
   <si>
     <t>FrontEnd</t>
   </si>
   <si>
-    <t>Zsemberi Izabella</t>
-  </si>
-  <si>
-    <t>Sötét Petra</t>
-  </si>
-  <si>
     <t>Adatb</t>
   </si>
   <si>
-    <t>Nagy Sz. Kamilla</t>
-  </si>
-  <si>
-    <t>Kovács Bence</t>
-  </si>
-  <si>
     <t>BackEnd</t>
-  </si>
-  <si>
-    <t>Fodor Döme</t>
   </si>
 </sst>
 </file>
@@ -327,7 +327,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,6 +384,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6D9EEB"/>
+        <bgColor rgb="FF6D9EEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
         <bgColor rgb="FFB6D7A8"/>
       </patternFill>
@@ -392,6 +398,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
         <bgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF674EA7"/>
+        <bgColor rgb="FF674EA7"/>
       </patternFill>
     </fill>
     <fill>
@@ -420,6 +432,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6FA8DC"/>
         <bgColor rgb="FF6FA8DC"/>
       </patternFill>
@@ -437,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -478,39 +496,41 @@
     <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="10" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="10" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="10" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="12" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="14" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="15" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="15" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="15" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="16" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="17" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="17" fontId="1" numFmtId="167" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -519,25 +539,28 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="18" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="14" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="13" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="11" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="12" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="16" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="19" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="17" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="20" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -754,6 +777,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="70.38"/>
+    <col customWidth="1" min="3" max="3" width="16.88"/>
     <col customWidth="1" min="4" max="4" width="13.75"/>
     <col customWidth="1" min="6" max="70" width="3.38"/>
   </cols>
@@ -1454,7 +1478,7 @@
       <c r="M9" s="13"/>
       <c r="N9" s="2"/>
       <c r="O9" s="16"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="16"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="13"/>
@@ -1528,7 +1552,7 @@
       <c r="M10" s="13"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
-      <c r="P10" s="2"/>
+      <c r="P10" s="18"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="13"/>
@@ -1586,12 +1610,12 @@
     </row>
     <row r="11">
       <c r="A11" s="2"/>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="16"/>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <v>45224.0</v>
       </c>
       <c r="F11" s="12"/>
@@ -1660,12 +1684,14 @@
     </row>
     <row r="12">
       <c r="A12" s="2"/>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="C12" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="12"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -1732,12 +1758,14 @@
     </row>
     <row r="13">
       <c r="A13" s="2"/>
-      <c r="B13" s="20" t="s">
-        <v>43</v>
+      <c r="B13" s="21" t="s">
+        <v>44</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="C13" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="12"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1804,12 +1832,14 @@
     </row>
     <row r="14">
       <c r="A14" s="2"/>
-      <c r="B14" s="20" t="s">
-        <v>44</v>
+      <c r="B14" s="21" t="s">
+        <v>46</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="C14" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="12"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1878,14 +1908,14 @@
     </row>
     <row r="15">
       <c r="A15" s="2"/>
-      <c r="B15" s="20" t="s">
-        <v>45</v>
+      <c r="B15" s="21" t="s">
+        <v>48</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>46</v>
+      <c r="C15" s="21" t="s">
+        <v>49</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="12"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1893,7 +1923,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="13"/>
-      <c r="M15" s="22"/>
+      <c r="M15" s="23"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1954,12 +1984,14 @@
     </row>
     <row r="16">
       <c r="A16" s="2"/>
-      <c r="B16" s="20" t="s">
-        <v>47</v>
+      <c r="B16" s="21" t="s">
+        <v>50</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="C16" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
       <c r="F16" s="12"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -2028,19 +2060,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2"/>
-      <c r="B17" s="20" t="s">
-        <v>48</v>
+      <c r="B17" s="21" t="s">
+        <v>52</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="C17" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="12"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="13"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
       <c r="M17" s="13"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2102,14 +2136,14 @@
     </row>
     <row r="18">
       <c r="A18" s="2"/>
-      <c r="B18" s="23" t="s">
-        <v>49</v>
+      <c r="B18" s="21" t="s">
+        <v>54</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="25">
-        <v>45245.0</v>
+      <c r="C18" s="21" t="s">
+        <v>55</v>
       </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
       <c r="F18" s="12"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -2178,20 +2212,20 @@
     </row>
     <row r="19">
       <c r="A19" s="2"/>
-      <c r="B19" s="26" t="s">
-        <v>50</v>
+      <c r="B19" s="25" t="s">
+        <v>56</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>51</v>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27">
+        <v>45245.0</v>
       </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
       <c r="F19" s="12"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
       <c r="N19" s="2"/>
@@ -2254,18 +2288,20 @@
     </row>
     <row r="20">
       <c r="A20" s="2"/>
-      <c r="B20" s="26" t="s">
-        <v>52</v>
+      <c r="B20" s="28" t="s">
+        <v>57</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="C20" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
       <c r="F20" s="12"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="2"/>
@@ -2328,12 +2364,14 @@
     </row>
     <row r="21">
       <c r="A21" s="2"/>
-      <c r="B21" s="26" t="s">
-        <v>53</v>
+      <c r="B21" s="28" t="s">
+        <v>58</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
+      <c r="C21" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
       <c r="F21" s="12"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -2402,14 +2440,17 @@
     </row>
     <row r="22">
       <c r="A22" s="2"/>
-      <c r="B22" s="26" t="s">
-        <v>54</v>
+      <c r="B22" s="28" t="s">
+        <v>59</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="C22" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
       <c r="F22" s="12"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -2475,15 +2516,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2"/>
-      <c r="B23" s="26" t="s">
-        <v>55</v>
+      <c r="B23" s="28" t="s">
+        <v>60</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
+      <c r="C23" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="12"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2549,14 +2591,17 @@
     </row>
     <row r="24">
       <c r="A24" s="2"/>
-      <c r="B24" s="26" t="s">
-        <v>56</v>
+      <c r="B24" s="28" t="s">
+        <v>61</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="C24" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
       <c r="F24" s="12"/>
       <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2622,15 +2667,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2"/>
-      <c r="B25" s="26" t="s">
-        <v>57</v>
+      <c r="B25" s="28" t="s">
+        <v>62</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
+      <c r="C25" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
       <c r="F25" s="12"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -2696,12 +2742,14 @@
     </row>
     <row r="26">
       <c r="A26" s="2"/>
-      <c r="B26" s="26" t="s">
-        <v>58</v>
+      <c r="B26" s="28" t="s">
+        <v>64</v>
       </c>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="C26" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
       <c r="F26" s="12"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -2770,12 +2818,14 @@
     </row>
     <row r="27">
       <c r="A27" s="2"/>
-      <c r="B27" s="26" t="s">
-        <v>59</v>
+      <c r="B27" s="28" t="s">
+        <v>65</v>
       </c>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
+      <c r="C27" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="12"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -2844,12 +2894,14 @@
     </row>
     <row r="28">
       <c r="A28" s="2"/>
-      <c r="B28" s="26" t="s">
-        <v>60</v>
+      <c r="B28" s="28" t="s">
+        <v>66</v>
       </c>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="C28" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
       <c r="F28" s="12"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -2918,12 +2970,14 @@
     </row>
     <row r="29">
       <c r="A29" s="2"/>
-      <c r="B29" s="26" t="s">
-        <v>61</v>
+      <c r="B29" s="28" t="s">
+        <v>67</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
+      <c r="C29" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
       <c r="F29" s="12"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -2992,12 +3046,14 @@
     </row>
     <row r="30">
       <c r="A30" s="2"/>
-      <c r="B30" s="26" t="s">
-        <v>62</v>
+      <c r="B30" s="28" t="s">
+        <v>68</v>
       </c>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="C30" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
       <c r="F30" s="12"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -3066,12 +3122,14 @@
     </row>
     <row r="31">
       <c r="A31" s="2"/>
-      <c r="B31" s="26" t="s">
-        <v>63</v>
+      <c r="B31" s="28" t="s">
+        <v>69</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
+      <c r="C31" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
       <c r="F31" s="12"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -3140,12 +3198,14 @@
     </row>
     <row r="32">
       <c r="A32" s="2"/>
-      <c r="B32" s="26" t="s">
-        <v>64</v>
+      <c r="B32" s="28" t="s">
+        <v>70</v>
       </c>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="C32" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="12"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -3214,12 +3274,14 @@
     </row>
     <row r="33">
       <c r="A33" s="2"/>
-      <c r="B33" s="26" t="s">
-        <v>65</v>
+      <c r="B33" s="28" t="s">
+        <v>71</v>
       </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="12"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -3287,13 +3349,15 @@
       <c r="BR33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="26" t="s">
-        <v>66</v>
+      <c r="A34" s="2"/>
+      <c r="B34" s="28" t="s">
+        <v>72</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
+      <c r="C34" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="12"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -3361,15 +3425,15 @@
       <c r="BR34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="2"/>
-      <c r="B35" s="26" t="s">
-        <v>67</v>
+      <c r="A35" s="1"/>
+      <c r="B35" s="28" t="s">
+        <v>73</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>38</v>
+      <c r="C35" s="28" t="s">
+        <v>43</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="12"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -3438,12 +3502,14 @@
     </row>
     <row r="36">
       <c r="A36" s="2"/>
-      <c r="B36" s="26" t="s">
-        <v>68</v>
+      <c r="B36" s="28" t="s">
+        <v>74</v>
       </c>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="C36" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
       <c r="F36" s="12"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -3512,14 +3578,14 @@
     </row>
     <row r="37">
       <c r="A37" s="2"/>
-      <c r="B37" s="29" t="s">
-        <v>69</v>
+      <c r="B37" s="28" t="s">
+        <v>75</v>
       </c>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="31">
-        <v>45266.0</v>
+      <c r="C37" s="28" t="s">
+        <v>53</v>
       </c>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="12"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -3588,12 +3654,14 @@
     </row>
     <row r="38">
       <c r="A38" s="2"/>
-      <c r="B38" s="32" t="s">
-        <v>70</v>
+      <c r="B38" s="31" t="s">
+        <v>76</v>
       </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="33">
+        <v>45266.0</v>
+      </c>
       <c r="F38" s="12"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -3662,12 +3730,14 @@
     </row>
     <row r="39">
       <c r="A39" s="2"/>
-      <c r="B39" s="32" t="s">
-        <v>71</v>
+      <c r="B39" s="34" t="s">
+        <v>77</v>
       </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
+      <c r="C39" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
       <c r="F39" s="12"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -3736,12 +3806,14 @@
     </row>
     <row r="40">
       <c r="A40" s="2"/>
-      <c r="B40" s="32" t="s">
-        <v>72</v>
+      <c r="B40" s="34" t="s">
+        <v>78</v>
       </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
+      <c r="C40" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
       <c r="F40" s="12"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -3810,12 +3882,14 @@
     </row>
     <row r="41">
       <c r="A41" s="2"/>
-      <c r="B41" s="32" t="s">
-        <v>73</v>
+      <c r="B41" s="34" t="s">
+        <v>79</v>
       </c>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
+      <c r="C41" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
       <c r="F41" s="12"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -3884,12 +3958,14 @@
     </row>
     <row r="42">
       <c r="A42" s="2"/>
-      <c r="B42" s="32" t="s">
-        <v>74</v>
+      <c r="B42" s="34" t="s">
+        <v>80</v>
       </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
+      <c r="C42" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
       <c r="F42" s="12"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -3958,12 +4034,14 @@
     </row>
     <row r="43">
       <c r="A43" s="2"/>
-      <c r="B43" s="32" t="s">
-        <v>75</v>
+      <c r="B43" s="34" t="s">
+        <v>81</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
+      <c r="C43" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
       <c r="F43" s="12"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -4032,12 +4110,14 @@
     </row>
     <row r="44">
       <c r="A44" s="2"/>
-      <c r="B44" s="32" t="s">
-        <v>76</v>
+      <c r="B44" s="34" t="s">
+        <v>82</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
+      <c r="C44" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
       <c r="F44" s="12"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -4106,12 +4186,14 @@
     </row>
     <row r="45">
       <c r="A45" s="2"/>
-      <c r="B45" s="32" t="s">
-        <v>77</v>
+      <c r="B45" s="34" t="s">
+        <v>83</v>
       </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
+      <c r="C45" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
       <c r="F45" s="12"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -4180,12 +4262,14 @@
     </row>
     <row r="46">
       <c r="A46" s="2"/>
-      <c r="B46" s="32" t="s">
-        <v>78</v>
+      <c r="B46" s="34" t="s">
+        <v>84</v>
       </c>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
+      <c r="C46" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
       <c r="F46" s="12"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -4254,12 +4338,14 @@
     </row>
     <row r="47">
       <c r="A47" s="2"/>
-      <c r="B47" s="32" t="s">
-        <v>79</v>
+      <c r="B47" s="34" t="s">
+        <v>85</v>
       </c>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
+      <c r="C47" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
       <c r="F47" s="12"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -4328,12 +4414,14 @@
     </row>
     <row r="48">
       <c r="A48" s="2"/>
-      <c r="B48" s="32" t="s">
-        <v>80</v>
+      <c r="B48" s="34" t="s">
+        <v>86</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="C48" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
       <c r="F48" s="12"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -4402,74 +4490,78 @@
     </row>
     <row r="49">
       <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="B49" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="12"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
-      <c r="S49" s="2"/>
-      <c r="T49" s="2"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="13"/>
       <c r="U49" s="2"/>
       <c r="V49" s="2"/>
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
       <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2"/>
+      <c r="Z49" s="13"/>
+      <c r="AA49" s="13"/>
       <c r="AB49" s="2"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="2"/>
       <c r="AE49" s="2"/>
       <c r="AF49" s="2"/>
-      <c r="AG49" s="2"/>
-      <c r="AH49" s="2"/>
+      <c r="AG49" s="13"/>
+      <c r="AH49" s="13"/>
       <c r="AI49" s="2"/>
       <c r="AJ49" s="2"/>
       <c r="AK49" s="2"/>
       <c r="AL49" s="2"/>
       <c r="AM49" s="2"/>
-      <c r="AN49" s="2"/>
-      <c r="AO49" s="2"/>
+      <c r="AN49" s="13"/>
+      <c r="AO49" s="13"/>
       <c r="AP49" s="2"/>
       <c r="AQ49" s="2"/>
       <c r="AR49" s="2"/>
       <c r="AS49" s="2"/>
       <c r="AT49" s="2"/>
-      <c r="AU49" s="2"/>
-      <c r="AV49" s="2"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="13"/>
       <c r="AW49" s="2"/>
       <c r="AX49" s="2"/>
       <c r="AY49" s="2"/>
       <c r="AZ49" s="2"/>
       <c r="BA49" s="2"/>
-      <c r="BB49" s="2"/>
-      <c r="BC49" s="2"/>
+      <c r="BB49" s="13"/>
+      <c r="BC49" s="13"/>
       <c r="BD49" s="2"/>
       <c r="BE49" s="2"/>
       <c r="BF49" s="2"/>
       <c r="BG49" s="2"/>
       <c r="BH49" s="2"/>
-      <c r="BI49" s="2"/>
-      <c r="BJ49" s="2"/>
+      <c r="BI49" s="13"/>
+      <c r="BJ49" s="13"/>
       <c r="BK49" s="2"/>
       <c r="BL49" s="2"/>
       <c r="BM49" s="2"/>
       <c r="BN49" s="2"/>
       <c r="BO49" s="2"/>
-      <c r="BP49" s="2"/>
-      <c r="BQ49" s="2"/>
+      <c r="BP49" s="13"/>
+      <c r="BQ49" s="13"/>
       <c r="BR49" s="2"/>
     </row>
     <row r="50">
@@ -4544,14 +4636,12 @@
       <c r="BQ50" s="2"/>
       <c r="BR50" s="2"/>
     </row>
-    <row r="51" ht="33.75" customHeight="1">
+    <row r="51">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="33"/>
-      <c r="E51" s="34"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -4619,167 +4709,165 @@
       <c r="BR51" s="2"/>
     </row>
     <row r="52" ht="33.75" customHeight="1">
-      <c r="A52" s="34"/>
-      <c r="B52" s="34"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
       <c r="C52" s="35" t="s">
-        <v>81</v>
+        <v>38</v>
       </c>
-      <c r="D52" s="35" t="s">
-        <v>82</v>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="3"/>
+      <c r="AD52" s="2"/>
+      <c r="AE52" s="2"/>
+      <c r="AF52" s="2"/>
+      <c r="AG52" s="2"/>
+      <c r="AH52" s="2"/>
+      <c r="AI52" s="2"/>
+      <c r="AJ52" s="2"/>
+      <c r="AK52" s="2"/>
+      <c r="AL52" s="2"/>
+      <c r="AM52" s="2"/>
+      <c r="AN52" s="2"/>
+      <c r="AO52" s="2"/>
+      <c r="AP52" s="2"/>
+      <c r="AQ52" s="2"/>
+      <c r="AR52" s="2"/>
+      <c r="AS52" s="2"/>
+      <c r="AT52" s="2"/>
+      <c r="AU52" s="2"/>
+      <c r="AV52" s="2"/>
+      <c r="AW52" s="2"/>
+      <c r="AX52" s="2"/>
+      <c r="AY52" s="2"/>
+      <c r="AZ52" s="2"/>
+      <c r="BA52" s="2"/>
+      <c r="BB52" s="2"/>
+      <c r="BC52" s="2"/>
+      <c r="BD52" s="2"/>
+      <c r="BE52" s="2"/>
+      <c r="BF52" s="2"/>
+      <c r="BG52" s="2"/>
+      <c r="BH52" s="2"/>
+      <c r="BI52" s="2"/>
+      <c r="BJ52" s="2"/>
+      <c r="BK52" s="2"/>
+      <c r="BL52" s="2"/>
+      <c r="BM52" s="2"/>
+      <c r="BN52" s="2"/>
+      <c r="BO52" s="2"/>
+      <c r="BP52" s="2"/>
+      <c r="BQ52" s="2"/>
+      <c r="BR52" s="2"/>
+    </row>
+    <row r="53" ht="33.75" customHeight="1">
+      <c r="A53" s="36"/>
+      <c r="B53" s="36"/>
+      <c r="C53" s="37" t="s">
+        <v>47</v>
       </c>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
-      <c r="I52" s="34"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
-      <c r="T52" s="34"/>
-      <c r="U52" s="34"/>
-      <c r="V52" s="34"/>
-      <c r="W52" s="34"/>
-      <c r="X52" s="34"/>
-      <c r="Y52" s="34"/>
-      <c r="Z52" s="34"/>
-      <c r="AA52" s="34"/>
-      <c r="AB52" s="34"/>
-      <c r="AC52" s="36"/>
-      <c r="AD52" s="34"/>
-      <c r="AE52" s="34"/>
-      <c r="AF52" s="34"/>
-      <c r="AG52" s="34"/>
-      <c r="AH52" s="34"/>
-      <c r="AI52" s="34"/>
-      <c r="AJ52" s="34"/>
-      <c r="AK52" s="34"/>
-      <c r="AL52" s="34"/>
-      <c r="AM52" s="34"/>
-      <c r="AN52" s="34"/>
-      <c r="AO52" s="34"/>
-      <c r="AP52" s="34"/>
-      <c r="AQ52" s="34"/>
-      <c r="AR52" s="34"/>
-      <c r="AS52" s="34"/>
-      <c r="AT52" s="34"/>
-      <c r="AU52" s="34"/>
-      <c r="AV52" s="34"/>
-      <c r="AW52" s="34"/>
-      <c r="AX52" s="34"/>
-      <c r="AY52" s="34"/>
-      <c r="AZ52" s="34"/>
-      <c r="BA52" s="34"/>
-      <c r="BB52" s="34"/>
-      <c r="BC52" s="34"/>
-      <c r="BD52" s="34"/>
-      <c r="BE52" s="34"/>
-      <c r="BF52" s="34"/>
-      <c r="BG52" s="34"/>
-      <c r="BH52" s="34"/>
-      <c r="BI52" s="34"/>
-      <c r="BJ52" s="34"/>
-      <c r="BK52" s="34"/>
-      <c r="BL52" s="34"/>
-      <c r="BM52" s="34"/>
-      <c r="BN52" s="34"/>
-      <c r="BO52" s="34"/>
-      <c r="BP52" s="34"/>
-      <c r="BQ52" s="34"/>
-      <c r="BR52" s="34"/>
-    </row>
-    <row r="53" ht="33.75" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="35" t="s">
-        <v>83</v>
+      <c r="D53" s="37" t="s">
+        <v>88</v>
       </c>
-      <c r="D53" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="2"/>
-      <c r="AA53" s="2"/>
-      <c r="AB53" s="2"/>
-      <c r="AC53" s="3"/>
-      <c r="AD53" s="2"/>
-      <c r="AE53" s="2"/>
-      <c r="AF53" s="2"/>
-      <c r="AG53" s="2"/>
-      <c r="AH53" s="2"/>
-      <c r="AI53" s="2"/>
-      <c r="AJ53" s="2"/>
-      <c r="AK53" s="2"/>
-      <c r="AL53" s="2"/>
-      <c r="AM53" s="2"/>
-      <c r="AN53" s="2"/>
-      <c r="AO53" s="2"/>
-      <c r="AP53" s="2"/>
-      <c r="AQ53" s="2"/>
-      <c r="AR53" s="2"/>
-      <c r="AS53" s="2"/>
-      <c r="AT53" s="2"/>
-      <c r="AU53" s="2"/>
-      <c r="AV53" s="2"/>
-      <c r="AW53" s="2"/>
-      <c r="AX53" s="2"/>
-      <c r="AY53" s="2"/>
-      <c r="AZ53" s="2"/>
-      <c r="BA53" s="2"/>
-      <c r="BB53" s="2"/>
-      <c r="BC53" s="2"/>
-      <c r="BD53" s="2"/>
-      <c r="BE53" s="2"/>
-      <c r="BF53" s="2"/>
-      <c r="BG53" s="2"/>
-      <c r="BH53" s="2"/>
-      <c r="BI53" s="2"/>
-      <c r="BJ53" s="2"/>
-      <c r="BK53" s="2"/>
-      <c r="BL53" s="2"/>
-      <c r="BM53" s="2"/>
-      <c r="BN53" s="2"/>
-      <c r="BO53" s="2"/>
-      <c r="BP53" s="2"/>
-      <c r="BQ53" s="2"/>
-      <c r="BR53" s="2"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="36"/>
+      <c r="U53" s="36"/>
+      <c r="V53" s="36"/>
+      <c r="W53" s="36"/>
+      <c r="X53" s="36"/>
+      <c r="Y53" s="36"/>
+      <c r="Z53" s="36"/>
+      <c r="AA53" s="36"/>
+      <c r="AB53" s="36"/>
+      <c r="AC53" s="38"/>
+      <c r="AD53" s="36"/>
+      <c r="AE53" s="36"/>
+      <c r="AF53" s="36"/>
+      <c r="AG53" s="36"/>
+      <c r="AH53" s="36"/>
+      <c r="AI53" s="36"/>
+      <c r="AJ53" s="36"/>
+      <c r="AK53" s="36"/>
+      <c r="AL53" s="36"/>
+      <c r="AM53" s="36"/>
+      <c r="AN53" s="36"/>
+      <c r="AO53" s="36"/>
+      <c r="AP53" s="36"/>
+      <c r="AQ53" s="36"/>
+      <c r="AR53" s="36"/>
+      <c r="AS53" s="36"/>
+      <c r="AT53" s="36"/>
+      <c r="AU53" s="36"/>
+      <c r="AV53" s="36"/>
+      <c r="AW53" s="36"/>
+      <c r="AX53" s="36"/>
+      <c r="AY53" s="36"/>
+      <c r="AZ53" s="36"/>
+      <c r="BA53" s="36"/>
+      <c r="BB53" s="36"/>
+      <c r="BC53" s="36"/>
+      <c r="BD53" s="36"/>
+      <c r="BE53" s="36"/>
+      <c r="BF53" s="36"/>
+      <c r="BG53" s="36"/>
+      <c r="BH53" s="36"/>
+      <c r="BI53" s="36"/>
+      <c r="BJ53" s="36"/>
+      <c r="BK53" s="36"/>
+      <c r="BL53" s="36"/>
+      <c r="BM53" s="36"/>
+      <c r="BN53" s="36"/>
+      <c r="BO53" s="36"/>
+      <c r="BP53" s="36"/>
+      <c r="BQ53" s="36"/>
+      <c r="BR53" s="36"/>
     </row>
     <row r="54" ht="33.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="37" t="s">
-        <v>85</v>
+      <c r="C54" s="39" t="s">
+        <v>53</v>
       </c>
-      <c r="D54" s="37" t="s">
-        <v>84</v>
+      <c r="D54" s="39" t="s">
+        <v>89</v>
       </c>
-      <c r="E54" s="34"/>
+      <c r="E54" s="36"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -4849,13 +4937,13 @@
     <row r="55" ht="33.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="38" t="s">
-        <v>86</v>
+      <c r="C55" s="40" t="s">
+        <v>51</v>
       </c>
-      <c r="D55" s="38" t="s">
-        <v>87</v>
+      <c r="D55" s="40" t="s">
+        <v>89</v>
       </c>
-      <c r="E55" s="34"/>
+      <c r="E55" s="36"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -4925,13 +5013,13 @@
     <row r="56" ht="33.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="39" t="s">
-        <v>88</v>
+      <c r="C56" s="41" t="s">
+        <v>49</v>
       </c>
-      <c r="D56" s="39" t="s">
-        <v>87</v>
+      <c r="D56" s="41" t="s">
+        <v>90</v>
       </c>
-      <c r="E56" s="34"/>
+      <c r="E56" s="36"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -5001,13 +5089,13 @@
     <row r="57" ht="33.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="40" t="s">
-        <v>89</v>
+      <c r="C57" s="42" t="s">
+        <v>55</v>
       </c>
-      <c r="D57" s="40" t="s">
+      <c r="D57" s="42" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="34"/>
+      <c r="E57" s="36"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -5077,13 +5165,13 @@
     <row r="58" ht="33.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
-      <c r="C58" s="41" t="s">
+      <c r="C58" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="34"/>
+      <c r="E58" s="36"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -5150,12 +5238,16 @@
       <c r="BQ58" s="2"/>
       <c r="BR58" s="2"/>
     </row>
-    <row r="59">
+    <row r="59" ht="33.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="C59" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="36"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -72974,6 +73066,78 @@
       <c r="BQ1000" s="2"/>
       <c r="BR1000" s="2"/>
     </row>
+    <row r="1001">
+      <c r="A1001" s="2"/>
+      <c r="B1001" s="2"/>
+      <c r="C1001" s="2"/>
+      <c r="D1001" s="2"/>
+      <c r="E1001" s="2"/>
+      <c r="F1001" s="2"/>
+      <c r="G1001" s="2"/>
+      <c r="H1001" s="2"/>
+      <c r="I1001" s="2"/>
+      <c r="J1001" s="2"/>
+      <c r="K1001" s="2"/>
+      <c r="L1001" s="2"/>
+      <c r="M1001" s="2"/>
+      <c r="N1001" s="2"/>
+      <c r="O1001" s="2"/>
+      <c r="P1001" s="2"/>
+      <c r="Q1001" s="2"/>
+      <c r="R1001" s="2"/>
+      <c r="S1001" s="2"/>
+      <c r="T1001" s="2"/>
+      <c r="U1001" s="2"/>
+      <c r="V1001" s="2"/>
+      <c r="W1001" s="2"/>
+      <c r="X1001" s="2"/>
+      <c r="Y1001" s="2"/>
+      <c r="Z1001" s="2"/>
+      <c r="AA1001" s="2"/>
+      <c r="AB1001" s="2"/>
+      <c r="AC1001" s="3"/>
+      <c r="AD1001" s="2"/>
+      <c r="AE1001" s="2"/>
+      <c r="AF1001" s="2"/>
+      <c r="AG1001" s="2"/>
+      <c r="AH1001" s="2"/>
+      <c r="AI1001" s="2"/>
+      <c r="AJ1001" s="2"/>
+      <c r="AK1001" s="2"/>
+      <c r="AL1001" s="2"/>
+      <c r="AM1001" s="2"/>
+      <c r="AN1001" s="2"/>
+      <c r="AO1001" s="2"/>
+      <c r="AP1001" s="2"/>
+      <c r="AQ1001" s="2"/>
+      <c r="AR1001" s="2"/>
+      <c r="AS1001" s="2"/>
+      <c r="AT1001" s="2"/>
+      <c r="AU1001" s="2"/>
+      <c r="AV1001" s="2"/>
+      <c r="AW1001" s="2"/>
+      <c r="AX1001" s="2"/>
+      <c r="AY1001" s="2"/>
+      <c r="AZ1001" s="2"/>
+      <c r="BA1001" s="2"/>
+      <c r="BB1001" s="2"/>
+      <c r="BC1001" s="2"/>
+      <c r="BD1001" s="2"/>
+      <c r="BE1001" s="2"/>
+      <c r="BF1001" s="2"/>
+      <c r="BG1001" s="2"/>
+      <c r="BH1001" s="2"/>
+      <c r="BI1001" s="2"/>
+      <c r="BJ1001" s="2"/>
+      <c r="BK1001" s="2"/>
+      <c r="BL1001" s="2"/>
+      <c r="BM1001" s="2"/>
+      <c r="BN1001" s="2"/>
+      <c r="BO1001" s="2"/>
+      <c r="BP1001" s="2"/>
+      <c r="BQ1001" s="2"/>
+      <c r="BR1001" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="BD6:BJ6"/>

--- a/M1/Gantt.xlsx
+++ b/M1/Gantt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ca5130f01ea323b/Egyetem/sem3/rf/2023_ib153i-11_d/M1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_9330639A7AF08A1872F30DB4C48058A071595D92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59E43291-3EC8-4E16-8B04-72CE38F39AD3}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="11_9330639A7AF08A1872F30DB4C48058A071595D92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34211C0B-BB84-4646-B434-DD53F39050D8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munkalap1" sheetId="1" r:id="rId1"/>
@@ -302,13 +302,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy\.\ mm\.\ dd\."/>
     <numFmt numFmtId="165" formatCode="yyyy\.\ mmm\ d\."/>
-    <numFmt numFmtId="166" formatCode="m\.\ d\."/>
-    <numFmt numFmtId="167" formatCode="mm\.\ dd\."/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -337,6 +336,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -474,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -486,22 +493,18 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -536,6 +539,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="169" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="5" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -551,6 +563,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1133,87 +1149,87 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="35">
+      <c r="G6" s="31">
         <v>45201</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="35">
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="31">
         <v>45208</v>
       </c>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="35">
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="31">
         <v>45215</v>
       </c>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="35">
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="31">
         <v>45222</v>
       </c>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="36"/>
-      <c r="AE6" s="36"/>
-      <c r="AF6" s="36"/>
-      <c r="AG6" s="36"/>
-      <c r="AH6" s="36"/>
-      <c r="AI6" s="35">
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="32"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="31">
         <v>45229</v>
       </c>
-      <c r="AJ6" s="36"/>
-      <c r="AK6" s="36"/>
-      <c r="AL6" s="36"/>
-      <c r="AM6" s="36"/>
-      <c r="AN6" s="36"/>
-      <c r="AO6" s="36"/>
-      <c r="AP6" s="35">
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="32"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="31">
         <v>45236</v>
       </c>
-      <c r="AQ6" s="36"/>
-      <c r="AR6" s="36"/>
-      <c r="AS6" s="36"/>
-      <c r="AT6" s="36"/>
-      <c r="AU6" s="36"/>
-      <c r="AV6" s="36"/>
-      <c r="AW6" s="35">
+      <c r="AQ6" s="32"/>
+      <c r="AR6" s="32"/>
+      <c r="AS6" s="32"/>
+      <c r="AT6" s="32"/>
+      <c r="AU6" s="32"/>
+      <c r="AV6" s="32"/>
+      <c r="AW6" s="31">
         <v>45243</v>
       </c>
-      <c r="AX6" s="36"/>
-      <c r="AY6" s="36"/>
-      <c r="AZ6" s="36"/>
-      <c r="BA6" s="36"/>
-      <c r="BB6" s="36"/>
-      <c r="BC6" s="36"/>
-      <c r="BD6" s="35">
+      <c r="AX6" s="32"/>
+      <c r="AY6" s="32"/>
+      <c r="AZ6" s="32"/>
+      <c r="BA6" s="32"/>
+      <c r="BB6" s="32"/>
+      <c r="BC6" s="32"/>
+      <c r="BD6" s="31">
         <v>45250</v>
       </c>
-      <c r="BE6" s="36"/>
-      <c r="BF6" s="36"/>
-      <c r="BG6" s="36"/>
-      <c r="BH6" s="36"/>
-      <c r="BI6" s="36"/>
-      <c r="BJ6" s="36"/>
-      <c r="BK6" s="35">
+      <c r="BE6" s="32"/>
+      <c r="BF6" s="32"/>
+      <c r="BG6" s="32"/>
+      <c r="BH6" s="32"/>
+      <c r="BI6" s="32"/>
+      <c r="BJ6" s="32"/>
+      <c r="BK6" s="31">
         <v>45257</v>
       </c>
-      <c r="BL6" s="36"/>
-      <c r="BM6" s="36"/>
-      <c r="BN6" s="36"/>
-      <c r="BO6" s="36"/>
-      <c r="BP6" s="36"/>
-      <c r="BQ6" s="36"/>
+      <c r="BL6" s="32"/>
+      <c r="BM6" s="32"/>
+      <c r="BN6" s="32"/>
+      <c r="BO6" s="32"/>
+      <c r="BP6" s="32"/>
+      <c r="BQ6" s="32"/>
       <c r="BR6" s="1"/>
     </row>
     <row r="7" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
@@ -1427,832 +1443,874 @@
         <v>36</v>
       </c>
       <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9">
+      <c r="D8" s="33">
+        <v>45196</v>
+      </c>
+      <c r="E8" s="33">
         <v>45210</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="10"/>
-      <c r="AO8" s="10"/>
+      <c r="AN8" s="9"/>
+      <c r="AO8" s="9"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="1"/>
       <c r="AR8" s="1"/>
       <c r="AS8" s="1"/>
       <c r="AT8" s="1"/>
-      <c r="AU8" s="10"/>
-      <c r="AV8" s="10"/>
+      <c r="AU8" s="9"/>
+      <c r="AV8" s="9"/>
       <c r="AW8" s="1"/>
       <c r="AX8" s="1"/>
       <c r="AY8" s="1"/>
       <c r="AZ8" s="1"/>
       <c r="BA8" s="1"/>
-      <c r="BB8" s="10"/>
-      <c r="BC8" s="10"/>
+      <c r="BB8" s="9"/>
+      <c r="BC8" s="9"/>
       <c r="BD8" s="1"/>
       <c r="BE8" s="1"/>
       <c r="BF8" s="1"/>
       <c r="BG8" s="1"/>
       <c r="BH8" s="1"/>
-      <c r="BI8" s="10"/>
-      <c r="BJ8" s="10"/>
+      <c r="BI8" s="9"/>
+      <c r="BJ8" s="9"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
       <c r="BM8" s="1"/>
       <c r="BN8" s="1"/>
       <c r="BO8" s="1"/>
-      <c r="BP8" s="10"/>
-      <c r="BQ8" s="10"/>
+      <c r="BP8" s="9"/>
+      <c r="BQ8" s="9"/>
       <c r="BR8" s="1"/>
     </row>
     <row r="9" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="D9" s="34">
+        <v>45208</v>
+      </c>
+      <c r="E9" s="34">
+        <v>45210</v>
+      </c>
       <c r="F9" s="6"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
       <c r="N9" s="1"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="10"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
-      <c r="AG9" s="10"/>
-      <c r="AH9" s="10"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="10"/>
-      <c r="AO9" s="10"/>
+      <c r="AN9" s="9"/>
+      <c r="AO9" s="9"/>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
       <c r="AR9" s="1"/>
       <c r="AS9" s="1"/>
       <c r="AT9" s="1"/>
-      <c r="AU9" s="10"/>
-      <c r="AV9" s="10"/>
+      <c r="AU9" s="9"/>
+      <c r="AV9" s="9"/>
       <c r="AW9" s="1"/>
       <c r="AX9" s="1"/>
       <c r="AY9" s="1"/>
       <c r="AZ9" s="1"/>
       <c r="BA9" s="1"/>
-      <c r="BB9" s="10"/>
-      <c r="BC9" s="10"/>
+      <c r="BB9" s="9"/>
+      <c r="BC9" s="9"/>
       <c r="BD9" s="1"/>
       <c r="BE9" s="1"/>
       <c r="BF9" s="1"/>
       <c r="BG9" s="1"/>
       <c r="BH9" s="1"/>
-      <c r="BI9" s="10"/>
-      <c r="BJ9" s="10"/>
+      <c r="BI9" s="9"/>
+      <c r="BJ9" s="9"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
       <c r="BM9" s="1"/>
       <c r="BN9" s="1"/>
       <c r="BO9" s="1"/>
-      <c r="BP9" s="10"/>
-      <c r="BQ9" s="10"/>
+      <c r="BP9" s="9"/>
+      <c r="BQ9" s="9"/>
       <c r="BR9" s="1"/>
     </row>
     <row r="10" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="D10" s="34">
+        <v>45208</v>
+      </c>
+      <c r="E10" s="34">
+        <v>45210</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="14"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="13"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
+      <c r="AG10" s="9"/>
+      <c r="AH10" s="9"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
-      <c r="AN10" s="10"/>
-      <c r="AO10" s="10"/>
+      <c r="AN10" s="9"/>
+      <c r="AO10" s="9"/>
       <c r="AP10" s="1"/>
       <c r="AQ10" s="1"/>
       <c r="AR10" s="1"/>
       <c r="AS10" s="1"/>
       <c r="AT10" s="1"/>
-      <c r="AU10" s="10"/>
-      <c r="AV10" s="10"/>
+      <c r="AU10" s="9"/>
+      <c r="AV10" s="9"/>
       <c r="AW10" s="1"/>
       <c r="AX10" s="1"/>
       <c r="AY10" s="1"/>
       <c r="AZ10" s="1"/>
       <c r="BA10" s="1"/>
-      <c r="BB10" s="10"/>
-      <c r="BC10" s="10"/>
+      <c r="BB10" s="9"/>
+      <c r="BC10" s="9"/>
       <c r="BD10" s="1"/>
       <c r="BE10" s="1"/>
       <c r="BF10" s="1"/>
       <c r="BG10" s="1"/>
       <c r="BH10" s="1"/>
-      <c r="BI10" s="10"/>
-      <c r="BJ10" s="10"/>
+      <c r="BI10" s="9"/>
+      <c r="BJ10" s="9"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
       <c r="BM10" s="1"/>
       <c r="BN10" s="1"/>
       <c r="BO10" s="1"/>
-      <c r="BP10" s="10"/>
-      <c r="BQ10" s="10"/>
+      <c r="BP10" s="9"/>
+      <c r="BQ10" s="9"/>
       <c r="BR10" s="1"/>
     </row>
     <row r="11" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="15">
+      <c r="C11" s="11"/>
+      <c r="D11" s="35">
+        <v>45211</v>
+      </c>
+      <c r="E11" s="35">
         <v>45224</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
-      <c r="Z11" s="10"/>
-      <c r="AA11" s="10"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
-      <c r="AG11" s="10"/>
-      <c r="AH11" s="10"/>
+      <c r="AG11" s="9"/>
+      <c r="AH11" s="9"/>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
-      <c r="AN11" s="10"/>
-      <c r="AO11" s="10"/>
+      <c r="AN11" s="9"/>
+      <c r="AO11" s="9"/>
       <c r="AP11" s="1"/>
       <c r="AQ11" s="1"/>
       <c r="AR11" s="1"/>
       <c r="AS11" s="1"/>
       <c r="AT11" s="1"/>
-      <c r="AU11" s="10"/>
-      <c r="AV11" s="10"/>
+      <c r="AU11" s="9"/>
+      <c r="AV11" s="9"/>
       <c r="AW11" s="1"/>
       <c r="AX11" s="1"/>
       <c r="AY11" s="1"/>
       <c r="AZ11" s="1"/>
       <c r="BA11" s="1"/>
-      <c r="BB11" s="10"/>
-      <c r="BC11" s="10"/>
+      <c r="BB11" s="9"/>
+      <c r="BC11" s="9"/>
       <c r="BD11" s="1"/>
       <c r="BE11" s="1"/>
       <c r="BF11" s="1"/>
       <c r="BG11" s="1"/>
       <c r="BH11" s="1"/>
-      <c r="BI11" s="10"/>
-      <c r="BJ11" s="10"/>
+      <c r="BI11" s="9"/>
+      <c r="BJ11" s="9"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
       <c r="BM11" s="1"/>
       <c r="BN11" s="1"/>
       <c r="BO11" s="1"/>
-      <c r="BP11" s="10"/>
-      <c r="BQ11" s="10"/>
+      <c r="BP11" s="9"/>
+      <c r="BQ11" s="9"/>
       <c r="BR11" s="1"/>
     </row>
     <row r="12" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
+      <c r="D12" s="36">
+        <v>45211</v>
+      </c>
+      <c r="E12" s="36">
+        <v>45213</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
+      <c r="AG12" s="9"/>
+      <c r="AH12" s="9"/>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="10"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1"/>
       <c r="AS12" s="1"/>
       <c r="AT12" s="1"/>
-      <c r="AU12" s="10"/>
-      <c r="AV12" s="10"/>
+      <c r="AU12" s="9"/>
+      <c r="AV12" s="9"/>
       <c r="AW12" s="1"/>
       <c r="AX12" s="1"/>
       <c r="AY12" s="1"/>
       <c r="AZ12" s="1"/>
       <c r="BA12" s="1"/>
-      <c r="BB12" s="10"/>
-      <c r="BC12" s="10"/>
+      <c r="BB12" s="9"/>
+      <c r="BC12" s="9"/>
       <c r="BD12" s="1"/>
       <c r="BE12" s="1"/>
       <c r="BF12" s="1"/>
       <c r="BG12" s="1"/>
       <c r="BH12" s="1"/>
-      <c r="BI12" s="10"/>
-      <c r="BJ12" s="10"/>
+      <c r="BI12" s="9"/>
+      <c r="BJ12" s="9"/>
       <c r="BK12" s="1"/>
       <c r="BL12" s="1"/>
       <c r="BM12" s="1"/>
       <c r="BN12" s="1"/>
       <c r="BO12" s="1"/>
-      <c r="BP12" s="10"/>
-      <c r="BQ12" s="10"/>
+      <c r="BP12" s="9"/>
+      <c r="BQ12" s="9"/>
       <c r="BR12" s="1"/>
     </row>
     <row r="13" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="36">
+        <v>45211</v>
+      </c>
+      <c r="E13" s="36">
+        <v>45213</v>
+      </c>
       <c r="F13" s="6"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="1"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
-      <c r="AG13" s="10"/>
-      <c r="AH13" s="10"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
-      <c r="AN13" s="10"/>
-      <c r="AO13" s="10"/>
+      <c r="AN13" s="9"/>
+      <c r="AO13" s="9"/>
       <c r="AP13" s="1"/>
       <c r="AQ13" s="1"/>
       <c r="AR13" s="1"/>
       <c r="AS13" s="1"/>
       <c r="AT13" s="1"/>
-      <c r="AU13" s="10"/>
-      <c r="AV13" s="10"/>
+      <c r="AU13" s="9"/>
+      <c r="AV13" s="9"/>
       <c r="AW13" s="1"/>
       <c r="AX13" s="1"/>
       <c r="AY13" s="1"/>
       <c r="AZ13" s="1"/>
       <c r="BA13" s="1"/>
-      <c r="BB13" s="10"/>
-      <c r="BC13" s="10"/>
+      <c r="BB13" s="9"/>
+      <c r="BC13" s="9"/>
       <c r="BD13" s="1"/>
       <c r="BE13" s="1"/>
       <c r="BF13" s="1"/>
       <c r="BG13" s="1"/>
       <c r="BH13" s="1"/>
-      <c r="BI13" s="10"/>
-      <c r="BJ13" s="10"/>
+      <c r="BI13" s="9"/>
+      <c r="BJ13" s="9"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
       <c r="BM13" s="1"/>
       <c r="BN13" s="1"/>
       <c r="BO13" s="1"/>
-      <c r="BP13" s="10"/>
-      <c r="BQ13" s="10"/>
+      <c r="BP13" s="9"/>
+      <c r="BQ13" s="9"/>
       <c r="BR13" s="1"/>
     </row>
     <row r="14" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="36">
+        <v>45213</v>
+      </c>
+      <c r="E14" s="36">
+        <v>45215</v>
+      </c>
       <c r="F14" s="6"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
+      <c r="Z14" s="9"/>
+      <c r="AA14" s="9"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="10"/>
+      <c r="AG14" s="9"/>
+      <c r="AH14" s="9"/>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
-      <c r="AN14" s="10"/>
-      <c r="AO14" s="10"/>
+      <c r="AN14" s="9"/>
+      <c r="AO14" s="9"/>
       <c r="AP14" s="1"/>
       <c r="AQ14" s="1"/>
       <c r="AR14" s="1"/>
       <c r="AS14" s="1"/>
       <c r="AT14" s="1"/>
-      <c r="AU14" s="10"/>
-      <c r="AV14" s="10"/>
+      <c r="AU14" s="9"/>
+      <c r="AV14" s="9"/>
       <c r="AW14" s="1"/>
       <c r="AX14" s="1"/>
       <c r="AY14" s="1"/>
       <c r="AZ14" s="1"/>
       <c r="BA14" s="1"/>
-      <c r="BB14" s="10"/>
-      <c r="BC14" s="10"/>
+      <c r="BB14" s="9"/>
+      <c r="BC14" s="9"/>
       <c r="BD14" s="1"/>
       <c r="BE14" s="1"/>
       <c r="BF14" s="1"/>
       <c r="BG14" s="1"/>
       <c r="BH14" s="1"/>
-      <c r="BI14" s="10"/>
-      <c r="BJ14" s="10"/>
+      <c r="BI14" s="9"/>
+      <c r="BJ14" s="9"/>
       <c r="BK14" s="1"/>
       <c r="BL14" s="1"/>
       <c r="BM14" s="1"/>
       <c r="BN14" s="1"/>
       <c r="BO14" s="1"/>
-      <c r="BP14" s="10"/>
-      <c r="BQ14" s="10"/>
+      <c r="BP14" s="9"/>
+      <c r="BQ14" s="9"/>
       <c r="BR14" s="1"/>
     </row>
     <row r="15" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="36">
+        <v>45207</v>
+      </c>
+      <c r="E15" s="36">
+        <v>45215</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="17"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="15"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
-      <c r="Z15" s="10"/>
-      <c r="AA15" s="10"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="1"/>
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
-      <c r="AG15" s="10"/>
-      <c r="AH15" s="10"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
-      <c r="AN15" s="10"/>
-      <c r="AO15" s="10"/>
+      <c r="AN15" s="9"/>
+      <c r="AO15" s="9"/>
       <c r="AP15" s="1"/>
       <c r="AQ15" s="1"/>
       <c r="AR15" s="1"/>
       <c r="AS15" s="1"/>
       <c r="AT15" s="1"/>
-      <c r="AU15" s="10"/>
-      <c r="AV15" s="10"/>
+      <c r="AU15" s="9"/>
+      <c r="AV15" s="9"/>
       <c r="AW15" s="1"/>
       <c r="AX15" s="1"/>
       <c r="AY15" s="1"/>
       <c r="AZ15" s="1"/>
       <c r="BA15" s="1"/>
-      <c r="BB15" s="10"/>
-      <c r="BC15" s="10"/>
+      <c r="BB15" s="9"/>
+      <c r="BC15" s="9"/>
       <c r="BD15" s="1"/>
       <c r="BE15" s="1"/>
       <c r="BF15" s="1"/>
       <c r="BG15" s="1"/>
       <c r="BH15" s="1"/>
-      <c r="BI15" s="10"/>
-      <c r="BJ15" s="10"/>
+      <c r="BI15" s="9"/>
+      <c r="BJ15" s="9"/>
       <c r="BK15" s="1"/>
       <c r="BL15" s="1"/>
       <c r="BM15" s="1"/>
       <c r="BN15" s="1"/>
       <c r="BO15" s="1"/>
-      <c r="BP15" s="10"/>
-      <c r="BQ15" s="10"/>
+      <c r="BP15" s="9"/>
+      <c r="BQ15" s="9"/>
       <c r="BR15" s="1"/>
     </row>
     <row r="16" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="36">
+        <v>45215</v>
+      </c>
+      <c r="E16" s="36">
+        <v>45218</v>
+      </c>
       <c r="F16" s="6"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="1"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="10"/>
+      <c r="AG16" s="9"/>
+      <c r="AH16" s="9"/>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
-      <c r="AN16" s="10"/>
-      <c r="AO16" s="10"/>
+      <c r="AN16" s="9"/>
+      <c r="AO16" s="9"/>
       <c r="AP16" s="1"/>
       <c r="AQ16" s="1"/>
       <c r="AR16" s="1"/>
       <c r="AS16" s="1"/>
       <c r="AT16" s="1"/>
-      <c r="AU16" s="10"/>
-      <c r="AV16" s="10"/>
+      <c r="AU16" s="9"/>
+      <c r="AV16" s="9"/>
       <c r="AW16" s="1"/>
       <c r="AX16" s="1"/>
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
       <c r="BA16" s="1"/>
-      <c r="BB16" s="10"/>
-      <c r="BC16" s="10"/>
+      <c r="BB16" s="9"/>
+      <c r="BC16" s="9"/>
       <c r="BD16" s="1"/>
       <c r="BE16" s="1"/>
       <c r="BF16" s="1"/>
       <c r="BG16" s="1"/>
       <c r="BH16" s="1"/>
-      <c r="BI16" s="10"/>
-      <c r="BJ16" s="10"/>
+      <c r="BI16" s="9"/>
+      <c r="BJ16" s="9"/>
       <c r="BK16" s="1"/>
       <c r="BL16" s="1"/>
       <c r="BM16" s="1"/>
       <c r="BN16" s="1"/>
       <c r="BO16" s="1"/>
-      <c r="BP16" s="10"/>
-      <c r="BQ16" s="10"/>
+      <c r="BP16" s="9"/>
+      <c r="BQ16" s="9"/>
       <c r="BR16" s="1"/>
     </row>
     <row r="17" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="36">
+        <v>45204</v>
+      </c>
+      <c r="E17" s="36">
+        <v>45221</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="10"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="9"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
-      <c r="Z17" s="10"/>
-      <c r="AA17" s="10"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="1"/>
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="10"/>
+      <c r="AG17" s="9"/>
+      <c r="AH17" s="9"/>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
-      <c r="AN17" s="10"/>
-      <c r="AO17" s="10"/>
+      <c r="AN17" s="9"/>
+      <c r="AO17" s="9"/>
       <c r="AP17" s="1"/>
       <c r="AQ17" s="1"/>
       <c r="AR17" s="1"/>
       <c r="AS17" s="1"/>
       <c r="AT17" s="1"/>
-      <c r="AU17" s="10"/>
-      <c r="AV17" s="10"/>
+      <c r="AU17" s="9"/>
+      <c r="AV17" s="9"/>
       <c r="AW17" s="1"/>
       <c r="AX17" s="1"/>
       <c r="AY17" s="1"/>
       <c r="AZ17" s="1"/>
       <c r="BA17" s="1"/>
-      <c r="BB17" s="10"/>
-      <c r="BC17" s="10"/>
+      <c r="BB17" s="9"/>
+      <c r="BC17" s="9"/>
       <c r="BD17" s="1"/>
       <c r="BE17" s="1"/>
       <c r="BF17" s="1"/>
       <c r="BG17" s="1"/>
       <c r="BH17" s="1"/>
-      <c r="BI17" s="10"/>
-      <c r="BJ17" s="10"/>
+      <c r="BI17" s="9"/>
+      <c r="BJ17" s="9"/>
       <c r="BK17" s="1"/>
       <c r="BL17" s="1"/>
       <c r="BM17" s="1"/>
       <c r="BN17" s="1"/>
       <c r="BO17" s="1"/>
-      <c r="BP17" s="10"/>
-      <c r="BQ17" s="10"/>
+      <c r="BP17" s="9"/>
+      <c r="BQ17" s="9"/>
       <c r="BR17" s="1"/>
     </row>
     <row r="18" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="D18" s="36">
+        <v>45221</v>
+      </c>
+      <c r="E18" s="36">
+        <v>45224</v>
+      </c>
       <c r="F18" s="6"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="2"/>
       <c r="AD18" s="1"/>
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
+      <c r="AG18" s="9"/>
+      <c r="AH18" s="9"/>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="10"/>
+      <c r="AN18" s="9"/>
+      <c r="AO18" s="9"/>
       <c r="AP18" s="1"/>
       <c r="AQ18" s="1"/>
       <c r="AR18" s="1"/>
       <c r="AS18" s="1"/>
       <c r="AT18" s="1"/>
-      <c r="AU18" s="10"/>
-      <c r="AV18" s="10"/>
+      <c r="AU18" s="9"/>
+      <c r="AV18" s="9"/>
       <c r="AW18" s="1"/>
       <c r="AX18" s="1"/>
       <c r="AY18" s="1"/>
       <c r="AZ18" s="1"/>
       <c r="BA18" s="1"/>
-      <c r="BB18" s="10"/>
-      <c r="BC18" s="10"/>
+      <c r="BB18" s="9"/>
+      <c r="BC18" s="9"/>
       <c r="BD18" s="1"/>
       <c r="BE18" s="1"/>
       <c r="BF18" s="1"/>
       <c r="BG18" s="1"/>
       <c r="BH18" s="1"/>
-      <c r="BI18" s="10"/>
-      <c r="BJ18" s="10"/>
+      <c r="BI18" s="9"/>
+      <c r="BJ18" s="9"/>
       <c r="BK18" s="1"/>
       <c r="BL18" s="1"/>
       <c r="BM18" s="1"/>
       <c r="BN18" s="1"/>
       <c r="BO18" s="1"/>
-      <c r="BP18" s="10"/>
-      <c r="BQ18" s="10"/>
+      <c r="BP18" s="9"/>
+      <c r="BQ18" s="9"/>
       <c r="BR18" s="1"/>
     </row>
     <row r="19" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20">
+      <c r="C19" s="17"/>
+      <c r="D19" s="37">
+        <v>45225</v>
+      </c>
+      <c r="E19" s="37">
         <v>45245</v>
       </c>
       <c r="F19" s="6"/>
@@ -2261,1440 +2319,1514 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
-      <c r="Z19" s="10"/>
-      <c r="AA19" s="10"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="2"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
-      <c r="AG19" s="10"/>
-      <c r="AH19" s="10"/>
+      <c r="AG19" s="9"/>
+      <c r="AH19" s="9"/>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
-      <c r="AN19" s="10"/>
-      <c r="AO19" s="10"/>
+      <c r="AN19" s="9"/>
+      <c r="AO19" s="9"/>
       <c r="AP19" s="1"/>
       <c r="AQ19" s="1"/>
       <c r="AR19" s="1"/>
       <c r="AS19" s="1"/>
       <c r="AT19" s="1"/>
-      <c r="AU19" s="10"/>
-      <c r="AV19" s="10"/>
+      <c r="AU19" s="9"/>
+      <c r="AV19" s="9"/>
       <c r="AW19" s="1"/>
       <c r="AX19" s="1"/>
       <c r="AY19" s="1"/>
       <c r="AZ19" s="1"/>
       <c r="BA19" s="1"/>
-      <c r="BB19" s="10"/>
-      <c r="BC19" s="10"/>
+      <c r="BB19" s="9"/>
+      <c r="BC19" s="9"/>
       <c r="BD19" s="1"/>
       <c r="BE19" s="1"/>
       <c r="BF19" s="1"/>
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
-      <c r="BI19" s="10"/>
-      <c r="BJ19" s="10"/>
+      <c r="BI19" s="9"/>
+      <c r="BJ19" s="9"/>
       <c r="BK19" s="1"/>
       <c r="BL19" s="1"/>
       <c r="BM19" s="1"/>
       <c r="BN19" s="1"/>
       <c r="BO19" s="1"/>
-      <c r="BP19" s="10"/>
-      <c r="BQ19" s="10"/>
+      <c r="BP19" s="9"/>
+      <c r="BQ19" s="9"/>
       <c r="BR19" s="1"/>
     </row>
     <row r="20" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="38">
+        <v>45204</v>
+      </c>
+      <c r="E20" s="38">
+        <v>45206</v>
+      </c>
       <c r="F20" s="6"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="1"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
+      <c r="Z20" s="9"/>
+      <c r="AA20" s="9"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
+      <c r="AG20" s="9"/>
+      <c r="AH20" s="9"/>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
-      <c r="AN20" s="10"/>
-      <c r="AO20" s="10"/>
+      <c r="AN20" s="9"/>
+      <c r="AO20" s="9"/>
       <c r="AP20" s="1"/>
       <c r="AQ20" s="1"/>
       <c r="AR20" s="1"/>
       <c r="AS20" s="1"/>
       <c r="AT20" s="1"/>
-      <c r="AU20" s="10"/>
-      <c r="AV20" s="10"/>
+      <c r="AU20" s="9"/>
+      <c r="AV20" s="9"/>
       <c r="AW20" s="1"/>
       <c r="AX20" s="1"/>
       <c r="AY20" s="1"/>
       <c r="AZ20" s="1"/>
       <c r="BA20" s="1"/>
-      <c r="BB20" s="10"/>
-      <c r="BC20" s="10"/>
+      <c r="BB20" s="9"/>
+      <c r="BC20" s="9"/>
       <c r="BD20" s="1"/>
       <c r="BE20" s="1"/>
       <c r="BF20" s="1"/>
       <c r="BG20" s="1"/>
       <c r="BH20" s="1"/>
-      <c r="BI20" s="10"/>
-      <c r="BJ20" s="10"/>
+      <c r="BI20" s="9"/>
+      <c r="BJ20" s="9"/>
       <c r="BK20" s="1"/>
       <c r="BL20" s="1"/>
       <c r="BM20" s="1"/>
       <c r="BN20" s="1"/>
       <c r="BO20" s="1"/>
-      <c r="BP20" s="10"/>
-      <c r="BQ20" s="10"/>
+      <c r="BP20" s="9"/>
+      <c r="BQ20" s="9"/>
       <c r="BR20" s="1"/>
     </row>
     <row r="21" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="38">
+        <v>45225</v>
+      </c>
+      <c r="E21" s="38">
+        <v>45227</v>
+      </c>
       <c r="F21" s="6"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="1"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
-      <c r="AG21" s="10"/>
-      <c r="AH21" s="10"/>
+      <c r="AG21" s="9"/>
+      <c r="AH21" s="9"/>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
-      <c r="AN21" s="10"/>
-      <c r="AO21" s="10"/>
+      <c r="AN21" s="9"/>
+      <c r="AO21" s="9"/>
       <c r="AP21" s="1"/>
       <c r="AQ21" s="1"/>
       <c r="AR21" s="1"/>
       <c r="AS21" s="1"/>
       <c r="AT21" s="1"/>
-      <c r="AU21" s="10"/>
-      <c r="AV21" s="10"/>
+      <c r="AU21" s="9"/>
+      <c r="AV21" s="9"/>
       <c r="AW21" s="1"/>
       <c r="AX21" s="1"/>
       <c r="AY21" s="1"/>
       <c r="AZ21" s="1"/>
       <c r="BA21" s="1"/>
-      <c r="BB21" s="10"/>
-      <c r="BC21" s="10"/>
+      <c r="BB21" s="9"/>
+      <c r="BC21" s="9"/>
       <c r="BD21" s="1"/>
       <c r="BE21" s="1"/>
       <c r="BF21" s="1"/>
       <c r="BG21" s="1"/>
       <c r="BH21" s="1"/>
-      <c r="BI21" s="10"/>
-      <c r="BJ21" s="10"/>
+      <c r="BI21" s="9"/>
+      <c r="BJ21" s="9"/>
       <c r="BK21" s="1"/>
       <c r="BL21" s="1"/>
       <c r="BM21" s="1"/>
       <c r="BN21" s="1"/>
       <c r="BO21" s="1"/>
-      <c r="BP21" s="10"/>
-      <c r="BQ21" s="10"/>
+      <c r="BP21" s="9"/>
+      <c r="BQ21" s="9"/>
       <c r="BR21" s="1"/>
     </row>
     <row r="22" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="38">
+        <v>45225</v>
+      </c>
+      <c r="E22" s="38">
+        <v>45227</v>
+      </c>
       <c r="F22" s="6"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="1"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
+      <c r="Z22" s="9"/>
+      <c r="AA22" s="9"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
-      <c r="AG22" s="10"/>
-      <c r="AH22" s="10"/>
+      <c r="AG22" s="9"/>
+      <c r="AH22" s="9"/>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
-      <c r="AN22" s="10"/>
-      <c r="AO22" s="10"/>
+      <c r="AN22" s="9"/>
+      <c r="AO22" s="9"/>
       <c r="AP22" s="1"/>
       <c r="AQ22" s="1"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
       <c r="AT22" s="1"/>
-      <c r="AU22" s="10"/>
-      <c r="AV22" s="10"/>
+      <c r="AU22" s="9"/>
+      <c r="AV22" s="9"/>
       <c r="AW22" s="1"/>
       <c r="AX22" s="1"/>
       <c r="AY22" s="1"/>
       <c r="AZ22" s="1"/>
       <c r="BA22" s="1"/>
-      <c r="BB22" s="10"/>
-      <c r="BC22" s="10"/>
+      <c r="BB22" s="9"/>
+      <c r="BC22" s="9"/>
       <c r="BD22" s="1"/>
       <c r="BE22" s="1"/>
       <c r="BF22" s="1"/>
       <c r="BG22" s="1"/>
       <c r="BH22" s="1"/>
-      <c r="BI22" s="10"/>
-      <c r="BJ22" s="10"/>
+      <c r="BI22" s="9"/>
+      <c r="BJ22" s="9"/>
       <c r="BK22" s="1"/>
       <c r="BL22" s="1"/>
       <c r="BM22" s="1"/>
       <c r="BN22" s="1"/>
       <c r="BO22" s="1"/>
-      <c r="BP22" s="10"/>
-      <c r="BQ22" s="10"/>
+      <c r="BP22" s="9"/>
+      <c r="BQ22" s="9"/>
       <c r="BR22" s="1"/>
     </row>
     <row r="23" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="38">
+        <v>45225</v>
+      </c>
+      <c r="E23" s="38">
+        <v>45227</v>
+      </c>
       <c r="F23" s="6"/>
       <c r="G23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
-      <c r="AN23" s="10"/>
-      <c r="AO23" s="10"/>
+      <c r="AN23" s="9"/>
+      <c r="AO23" s="9"/>
       <c r="AP23" s="1"/>
       <c r="AQ23" s="1"/>
       <c r="AR23" s="1"/>
       <c r="AS23" s="1"/>
       <c r="AT23" s="1"/>
-      <c r="AU23" s="10"/>
-      <c r="AV23" s="10"/>
+      <c r="AU23" s="9"/>
+      <c r="AV23" s="9"/>
       <c r="AW23" s="1"/>
       <c r="AX23" s="1"/>
       <c r="AY23" s="1"/>
       <c r="AZ23" s="1"/>
       <c r="BA23" s="1"/>
-      <c r="BB23" s="10"/>
-      <c r="BC23" s="10"/>
+      <c r="BB23" s="9"/>
+      <c r="BC23" s="9"/>
       <c r="BD23" s="1"/>
       <c r="BE23" s="1"/>
       <c r="BF23" s="1"/>
       <c r="BG23" s="1"/>
       <c r="BH23" s="1"/>
-      <c r="BI23" s="10"/>
-      <c r="BJ23" s="10"/>
+      <c r="BI23" s="9"/>
+      <c r="BJ23" s="9"/>
       <c r="BK23" s="1"/>
       <c r="BL23" s="1"/>
       <c r="BM23" s="1"/>
       <c r="BN23" s="1"/>
       <c r="BO23" s="1"/>
-      <c r="BP23" s="10"/>
-      <c r="BQ23" s="10"/>
+      <c r="BP23" s="9"/>
+      <c r="BQ23" s="9"/>
       <c r="BR23" s="1"/>
     </row>
     <row r="24" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="38">
+        <v>45227</v>
+      </c>
+      <c r="E24" s="38">
+        <v>45231</v>
+      </c>
       <c r="F24" s="6"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="1"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
+      <c r="Z24" s="9"/>
+      <c r="AA24" s="9"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="10"/>
+      <c r="AG24" s="9"/>
+      <c r="AH24" s="9"/>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
-      <c r="AN24" s="10"/>
-      <c r="AO24" s="10"/>
+      <c r="AN24" s="9"/>
+      <c r="AO24" s="9"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
       <c r="AR24" s="1"/>
       <c r="AS24" s="1"/>
       <c r="AT24" s="1"/>
-      <c r="AU24" s="10"/>
-      <c r="AV24" s="10"/>
+      <c r="AU24" s="9"/>
+      <c r="AV24" s="9"/>
       <c r="AW24" s="1"/>
       <c r="AX24" s="1"/>
       <c r="AY24" s="1"/>
       <c r="AZ24" s="1"/>
       <c r="BA24" s="1"/>
-      <c r="BB24" s="10"/>
-      <c r="BC24" s="10"/>
+      <c r="BB24" s="9"/>
+      <c r="BC24" s="9"/>
       <c r="BD24" s="1"/>
       <c r="BE24" s="1"/>
       <c r="BF24" s="1"/>
       <c r="BG24" s="1"/>
       <c r="BH24" s="1"/>
-      <c r="BI24" s="10"/>
-      <c r="BJ24" s="10"/>
+      <c r="BI24" s="9"/>
+      <c r="BJ24" s="9"/>
       <c r="BK24" s="1"/>
       <c r="BL24" s="1"/>
       <c r="BM24" s="1"/>
       <c r="BN24" s="1"/>
       <c r="BO24" s="1"/>
-      <c r="BP24" s="10"/>
-      <c r="BQ24" s="10"/>
+      <c r="BP24" s="9"/>
+      <c r="BQ24" s="9"/>
       <c r="BR24" s="1"/>
     </row>
     <row r="25" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
+      <c r="D25" s="38">
+        <v>45227</v>
+      </c>
+      <c r="E25" s="38">
+        <v>45231</v>
+      </c>
       <c r="F25" s="6"/>
       <c r="G25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
-      <c r="Z25" s="10"/>
-      <c r="AA25" s="10"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="2"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
-      <c r="AG25" s="10"/>
-      <c r="AH25" s="10"/>
+      <c r="AG25" s="9"/>
+      <c r="AH25" s="9"/>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
-      <c r="AN25" s="10"/>
-      <c r="AO25" s="10"/>
+      <c r="AN25" s="9"/>
+      <c r="AO25" s="9"/>
       <c r="AP25" s="1"/>
       <c r="AQ25" s="1"/>
       <c r="AR25" s="1"/>
       <c r="AS25" s="1"/>
       <c r="AT25" s="1"/>
-      <c r="AU25" s="10"/>
-      <c r="AV25" s="10"/>
+      <c r="AU25" s="9"/>
+      <c r="AV25" s="9"/>
       <c r="AW25" s="1"/>
       <c r="AX25" s="1"/>
       <c r="AY25" s="1"/>
       <c r="AZ25" s="1"/>
       <c r="BA25" s="1"/>
-      <c r="BB25" s="10"/>
-      <c r="BC25" s="10"/>
+      <c r="BB25" s="9"/>
+      <c r="BC25" s="9"/>
       <c r="BD25" s="1"/>
       <c r="BE25" s="1"/>
       <c r="BF25" s="1"/>
       <c r="BG25" s="1"/>
       <c r="BH25" s="1"/>
-      <c r="BI25" s="10"/>
-      <c r="BJ25" s="10"/>
+      <c r="BI25" s="9"/>
+      <c r="BJ25" s="9"/>
       <c r="BK25" s="1"/>
       <c r="BL25" s="1"/>
       <c r="BM25" s="1"/>
       <c r="BN25" s="1"/>
       <c r="BO25" s="1"/>
-      <c r="BP25" s="10"/>
-      <c r="BQ25" s="10"/>
+      <c r="BP25" s="9"/>
+      <c r="BQ25" s="9"/>
       <c r="BR25" s="1"/>
     </row>
     <row r="26" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="38">
+        <v>45232</v>
+      </c>
+      <c r="E26" s="38">
+        <v>45234</v>
+      </c>
       <c r="F26" s="6"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
+      <c r="Z26" s="9"/>
+      <c r="AA26" s="9"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="1"/>
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
-      <c r="AG26" s="10"/>
-      <c r="AH26" s="10"/>
+      <c r="AG26" s="9"/>
+      <c r="AH26" s="9"/>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
-      <c r="AN26" s="10"/>
-      <c r="AO26" s="10"/>
+      <c r="AN26" s="9"/>
+      <c r="AO26" s="9"/>
       <c r="AP26" s="1"/>
       <c r="AQ26" s="1"/>
       <c r="AR26" s="1"/>
       <c r="AS26" s="1"/>
       <c r="AT26" s="1"/>
-      <c r="AU26" s="10"/>
-      <c r="AV26" s="10"/>
+      <c r="AU26" s="9"/>
+      <c r="AV26" s="9"/>
       <c r="AW26" s="1"/>
       <c r="AX26" s="1"/>
       <c r="AY26" s="1"/>
       <c r="AZ26" s="1"/>
       <c r="BA26" s="1"/>
-      <c r="BB26" s="10"/>
-      <c r="BC26" s="10"/>
+      <c r="BB26" s="9"/>
+      <c r="BC26" s="9"/>
       <c r="BD26" s="1"/>
       <c r="BE26" s="1"/>
       <c r="BF26" s="1"/>
       <c r="BG26" s="1"/>
       <c r="BH26" s="1"/>
-      <c r="BI26" s="10"/>
-      <c r="BJ26" s="10"/>
+      <c r="BI26" s="9"/>
+      <c r="BJ26" s="9"/>
       <c r="BK26" s="1"/>
       <c r="BL26" s="1"/>
       <c r="BM26" s="1"/>
       <c r="BN26" s="1"/>
       <c r="BO26" s="1"/>
-      <c r="BP26" s="10"/>
-      <c r="BQ26" s="10"/>
+      <c r="BP26" s="9"/>
+      <c r="BQ26" s="9"/>
       <c r="BR26" s="1"/>
     </row>
     <row r="27" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="38">
+        <v>45232</v>
+      </c>
+      <c r="E27" s="38">
+        <v>45234</v>
+      </c>
       <c r="F27" s="6"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
-      <c r="Z27" s="10"/>
-      <c r="AA27" s="10"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AG27" s="10"/>
-      <c r="AH27" s="10"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9"/>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
-      <c r="AN27" s="10"/>
-      <c r="AO27" s="10"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
       <c r="AR27" s="1"/>
       <c r="AS27" s="1"/>
       <c r="AT27" s="1"/>
-      <c r="AU27" s="10"/>
-      <c r="AV27" s="10"/>
+      <c r="AU27" s="9"/>
+      <c r="AV27" s="9"/>
       <c r="AW27" s="1"/>
       <c r="AX27" s="1"/>
       <c r="AY27" s="1"/>
       <c r="AZ27" s="1"/>
       <c r="BA27" s="1"/>
-      <c r="BB27" s="10"/>
-      <c r="BC27" s="10"/>
+      <c r="BB27" s="9"/>
+      <c r="BC27" s="9"/>
       <c r="BD27" s="1"/>
       <c r="BE27" s="1"/>
       <c r="BF27" s="1"/>
       <c r="BG27" s="1"/>
       <c r="BH27" s="1"/>
-      <c r="BI27" s="10"/>
-      <c r="BJ27" s="10"/>
+      <c r="BI27" s="9"/>
+      <c r="BJ27" s="9"/>
       <c r="BK27" s="1"/>
       <c r="BL27" s="1"/>
       <c r="BM27" s="1"/>
       <c r="BN27" s="1"/>
       <c r="BO27" s="1"/>
-      <c r="BP27" s="10"/>
-      <c r="BQ27" s="10"/>
+      <c r="BP27" s="9"/>
+      <c r="BQ27" s="9"/>
       <c r="BR27" s="1"/>
     </row>
     <row r="28" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="D28" s="38">
+        <v>45232</v>
+      </c>
+      <c r="E28" s="38">
+        <v>45234</v>
+      </c>
       <c r="F28" s="6"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-      <c r="Z28" s="10"/>
-      <c r="AA28" s="10"/>
+      <c r="Z28" s="9"/>
+      <c r="AA28" s="9"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
-      <c r="AG28" s="10"/>
-      <c r="AH28" s="10"/>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
       <c r="AM28" s="1"/>
-      <c r="AN28" s="10"/>
-      <c r="AO28" s="10"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
       <c r="AR28" s="1"/>
       <c r="AS28" s="1"/>
       <c r="AT28" s="1"/>
-      <c r="AU28" s="10"/>
-      <c r="AV28" s="10"/>
+      <c r="AU28" s="9"/>
+      <c r="AV28" s="9"/>
       <c r="AW28" s="1"/>
       <c r="AX28" s="1"/>
       <c r="AY28" s="1"/>
       <c r="AZ28" s="1"/>
       <c r="BA28" s="1"/>
-      <c r="BB28" s="10"/>
-      <c r="BC28" s="10"/>
+      <c r="BB28" s="9"/>
+      <c r="BC28" s="9"/>
       <c r="BD28" s="1"/>
       <c r="BE28" s="1"/>
       <c r="BF28" s="1"/>
       <c r="BG28" s="1"/>
       <c r="BH28" s="1"/>
-      <c r="BI28" s="10"/>
-      <c r="BJ28" s="10"/>
+      <c r="BI28" s="9"/>
+      <c r="BJ28" s="9"/>
       <c r="BK28" s="1"/>
       <c r="BL28" s="1"/>
       <c r="BM28" s="1"/>
       <c r="BN28" s="1"/>
       <c r="BO28" s="1"/>
-      <c r="BP28" s="10"/>
-      <c r="BQ28" s="10"/>
+      <c r="BP28" s="9"/>
+      <c r="BQ28" s="9"/>
       <c r="BR28" s="1"/>
     </row>
     <row r="29" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
+      <c r="D29" s="38">
+        <v>45232</v>
+      </c>
+      <c r="E29" s="38">
+        <v>45234</v>
+      </c>
       <c r="F29" s="6"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
       <c r="U29" s="1"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
-      <c r="Z29" s="10"/>
-      <c r="AA29" s="10"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="2"/>
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="10"/>
-      <c r="AH29" s="10"/>
+      <c r="AG29" s="9"/>
+      <c r="AH29" s="9"/>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
-      <c r="AN29" s="10"/>
-      <c r="AO29" s="10"/>
+      <c r="AN29" s="9"/>
+      <c r="AO29" s="9"/>
       <c r="AP29" s="1"/>
       <c r="AQ29" s="1"/>
       <c r="AR29" s="1"/>
       <c r="AS29" s="1"/>
       <c r="AT29" s="1"/>
-      <c r="AU29" s="10"/>
-      <c r="AV29" s="10"/>
+      <c r="AU29" s="9"/>
+      <c r="AV29" s="9"/>
       <c r="AW29" s="1"/>
       <c r="AX29" s="1"/>
       <c r="AY29" s="1"/>
       <c r="AZ29" s="1"/>
       <c r="BA29" s="1"/>
-      <c r="BB29" s="10"/>
-      <c r="BC29" s="10"/>
+      <c r="BB29" s="9"/>
+      <c r="BC29" s="9"/>
       <c r="BD29" s="1"/>
       <c r="BE29" s="1"/>
       <c r="BF29" s="1"/>
       <c r="BG29" s="1"/>
       <c r="BH29" s="1"/>
-      <c r="BI29" s="10"/>
-      <c r="BJ29" s="10"/>
+      <c r="BI29" s="9"/>
+      <c r="BJ29" s="9"/>
       <c r="BK29" s="1"/>
       <c r="BL29" s="1"/>
       <c r="BM29" s="1"/>
       <c r="BN29" s="1"/>
       <c r="BO29" s="1"/>
-      <c r="BP29" s="10"/>
-      <c r="BQ29" s="10"/>
+      <c r="BP29" s="9"/>
+      <c r="BQ29" s="9"/>
       <c r="BR29" s="1"/>
     </row>
     <row r="30" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
+      <c r="D30" s="38">
+        <v>45234</v>
+      </c>
+      <c r="E30" s="38">
+        <v>45237</v>
+      </c>
       <c r="F30" s="6"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
       <c r="U30" s="1"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10"/>
+      <c r="Z30" s="9"/>
+      <c r="AA30" s="9"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
-      <c r="AG30" s="10"/>
-      <c r="AH30" s="10"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
-      <c r="AN30" s="10"/>
-      <c r="AO30" s="10"/>
+      <c r="AN30" s="9"/>
+      <c r="AO30" s="9"/>
       <c r="AP30" s="1"/>
       <c r="AQ30" s="1"/>
       <c r="AR30" s="1"/>
       <c r="AS30" s="1"/>
       <c r="AT30" s="1"/>
-      <c r="AU30" s="10"/>
-      <c r="AV30" s="10"/>
+      <c r="AU30" s="9"/>
+      <c r="AV30" s="9"/>
       <c r="AW30" s="1"/>
       <c r="AX30" s="1"/>
       <c r="AY30" s="1"/>
       <c r="AZ30" s="1"/>
       <c r="BA30" s="1"/>
-      <c r="BB30" s="10"/>
-      <c r="BC30" s="10"/>
+      <c r="BB30" s="9"/>
+      <c r="BC30" s="9"/>
       <c r="BD30" s="1"/>
       <c r="BE30" s="1"/>
       <c r="BF30" s="1"/>
       <c r="BG30" s="1"/>
       <c r="BH30" s="1"/>
-      <c r="BI30" s="10"/>
-      <c r="BJ30" s="10"/>
+      <c r="BI30" s="9"/>
+      <c r="BJ30" s="9"/>
       <c r="BK30" s="1"/>
       <c r="BL30" s="1"/>
       <c r="BM30" s="1"/>
       <c r="BN30" s="1"/>
       <c r="BO30" s="1"/>
-      <c r="BP30" s="10"/>
-      <c r="BQ30" s="10"/>
+      <c r="BP30" s="9"/>
+      <c r="BQ30" s="9"/>
       <c r="BR30" s="1"/>
     </row>
     <row r="31" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="D31" s="38">
+        <v>45235</v>
+      </c>
+      <c r="E31" s="38">
+        <v>45237</v>
+      </c>
       <c r="F31" s="6"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
       <c r="U31" s="1"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="10"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="10"/>
-      <c r="AH31" s="10"/>
+      <c r="AG31" s="9"/>
+      <c r="AH31" s="9"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
-      <c r="AN31" s="10"/>
-      <c r="AO31" s="10"/>
+      <c r="AN31" s="9"/>
+      <c r="AO31" s="9"/>
       <c r="AP31" s="1"/>
       <c r="AQ31" s="1"/>
       <c r="AR31" s="1"/>
       <c r="AS31" s="1"/>
       <c r="AT31" s="1"/>
-      <c r="AU31" s="10"/>
-      <c r="AV31" s="10"/>
+      <c r="AU31" s="9"/>
+      <c r="AV31" s="9"/>
       <c r="AW31" s="1"/>
       <c r="AX31" s="1"/>
       <c r="AY31" s="1"/>
       <c r="AZ31" s="1"/>
       <c r="BA31" s="1"/>
-      <c r="BB31" s="10"/>
-      <c r="BC31" s="10"/>
+      <c r="BB31" s="9"/>
+      <c r="BC31" s="9"/>
       <c r="BD31" s="1"/>
       <c r="BE31" s="1"/>
       <c r="BF31" s="1"/>
       <c r="BG31" s="1"/>
       <c r="BH31" s="1"/>
-      <c r="BI31" s="10"/>
-      <c r="BJ31" s="10"/>
+      <c r="BI31" s="9"/>
+      <c r="BJ31" s="9"/>
       <c r="BK31" s="1"/>
       <c r="BL31" s="1"/>
       <c r="BM31" s="1"/>
       <c r="BN31" s="1"/>
       <c r="BO31" s="1"/>
-      <c r="BP31" s="10"/>
-      <c r="BQ31" s="10"/>
+      <c r="BP31" s="9"/>
+      <c r="BQ31" s="9"/>
       <c r="BR31" s="1"/>
     </row>
     <row r="32" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
+      <c r="D32" s="38">
+        <v>45235</v>
+      </c>
+      <c r="E32" s="38">
+        <v>45237</v>
+      </c>
       <c r="F32" s="6"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="10"/>
+      <c r="Z32" s="9"/>
+      <c r="AA32" s="9"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
-      <c r="AG32" s="10"/>
-      <c r="AH32" s="10"/>
+      <c r="AG32" s="9"/>
+      <c r="AH32" s="9"/>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
-      <c r="AN32" s="10"/>
-      <c r="AO32" s="10"/>
+      <c r="AN32" s="9"/>
+      <c r="AO32" s="9"/>
       <c r="AP32" s="1"/>
       <c r="AQ32" s="1"/>
       <c r="AR32" s="1"/>
       <c r="AS32" s="1"/>
       <c r="AT32" s="1"/>
-      <c r="AU32" s="10"/>
-      <c r="AV32" s="10"/>
+      <c r="AU32" s="9"/>
+      <c r="AV32" s="9"/>
       <c r="AW32" s="1"/>
       <c r="AX32" s="1"/>
       <c r="AY32" s="1"/>
       <c r="AZ32" s="1"/>
       <c r="BA32" s="1"/>
-      <c r="BB32" s="10"/>
-      <c r="BC32" s="10"/>
+      <c r="BB32" s="9"/>
+      <c r="BC32" s="9"/>
       <c r="BD32" s="1"/>
       <c r="BE32" s="1"/>
       <c r="BF32" s="1"/>
       <c r="BG32" s="1"/>
       <c r="BH32" s="1"/>
-      <c r="BI32" s="10"/>
-      <c r="BJ32" s="10"/>
+      <c r="BI32" s="9"/>
+      <c r="BJ32" s="9"/>
       <c r="BK32" s="1"/>
       <c r="BL32" s="1"/>
       <c r="BM32" s="1"/>
       <c r="BN32" s="1"/>
       <c r="BO32" s="1"/>
-      <c r="BP32" s="10"/>
-      <c r="BQ32" s="10"/>
+      <c r="BP32" s="9"/>
+      <c r="BQ32" s="9"/>
       <c r="BR32" s="1"/>
     </row>
     <row r="33" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
+      <c r="D33" s="38">
+        <v>45235</v>
+      </c>
+      <c r="E33" s="38">
+        <v>45237</v>
+      </c>
       <c r="F33" s="6"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
       <c r="U33" s="1"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
-      <c r="Z33" s="10"/>
-      <c r="AA33" s="10"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="10"/>
-      <c r="AH33" s="10"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
-      <c r="AN33" s="10"/>
-      <c r="AO33" s="10"/>
+      <c r="AN33" s="9"/>
+      <c r="AO33" s="9"/>
       <c r="AP33" s="1"/>
       <c r="AQ33" s="1"/>
       <c r="AR33" s="1"/>
       <c r="AS33" s="1"/>
       <c r="AT33" s="1"/>
-      <c r="AU33" s="10"/>
-      <c r="AV33" s="10"/>
+      <c r="AU33" s="9"/>
+      <c r="AV33" s="9"/>
       <c r="AW33" s="1"/>
       <c r="AX33" s="1"/>
       <c r="AY33" s="1"/>
       <c r="AZ33" s="1"/>
       <c r="BA33" s="1"/>
-      <c r="BB33" s="10"/>
-      <c r="BC33" s="10"/>
+      <c r="BB33" s="9"/>
+      <c r="BC33" s="9"/>
       <c r="BD33" s="1"/>
       <c r="BE33" s="1"/>
       <c r="BF33" s="1"/>
       <c r="BG33" s="1"/>
       <c r="BH33" s="1"/>
-      <c r="BI33" s="10"/>
-      <c r="BJ33" s="10"/>
+      <c r="BI33" s="9"/>
+      <c r="BJ33" s="9"/>
       <c r="BK33" s="1"/>
       <c r="BL33" s="1"/>
       <c r="BM33" s="1"/>
       <c r="BN33" s="1"/>
       <c r="BO33" s="1"/>
-      <c r="BP33" s="10"/>
-      <c r="BQ33" s="10"/>
+      <c r="BP33" s="9"/>
+      <c r="BQ33" s="9"/>
       <c r="BR33" s="1"/>
     </row>
     <row r="34" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
+      <c r="D34" s="41">
+        <v>45238</v>
+      </c>
+      <c r="E34" s="38">
+        <v>45240</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
       <c r="U34" s="1"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10"/>
+      <c r="Z34" s="9"/>
+      <c r="AA34" s="9"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
-      <c r="AG34" s="10"/>
-      <c r="AH34" s="10"/>
+      <c r="AG34" s="9"/>
+      <c r="AH34" s="9"/>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
-      <c r="AN34" s="10"/>
-      <c r="AO34" s="10"/>
+      <c r="AN34" s="9"/>
+      <c r="AO34" s="9"/>
       <c r="AP34" s="1"/>
       <c r="AQ34" s="1"/>
       <c r="AR34" s="1"/>
       <c r="AS34" s="1"/>
       <c r="AT34" s="1"/>
-      <c r="AU34" s="10"/>
-      <c r="AV34" s="10"/>
+      <c r="AU34" s="9"/>
+      <c r="AV34" s="9"/>
       <c r="AW34" s="1"/>
       <c r="AX34" s="1"/>
       <c r="AY34" s="1"/>
       <c r="AZ34" s="1"/>
       <c r="BA34" s="1"/>
-      <c r="BB34" s="10"/>
-      <c r="BC34" s="10"/>
+      <c r="BB34" s="9"/>
+      <c r="BC34" s="9"/>
       <c r="BD34" s="1"/>
       <c r="BE34" s="1"/>
       <c r="BF34" s="1"/>
       <c r="BG34" s="1"/>
       <c r="BH34" s="1"/>
-      <c r="BI34" s="10"/>
-      <c r="BJ34" s="10"/>
+      <c r="BI34" s="9"/>
+      <c r="BJ34" s="9"/>
       <c r="BK34" s="1"/>
       <c r="BL34" s="1"/>
       <c r="BM34" s="1"/>
       <c r="BN34" s="1"/>
       <c r="BO34" s="1"/>
-      <c r="BP34" s="10"/>
-      <c r="BQ34" s="10"/>
+      <c r="BP34" s="9"/>
+      <c r="BQ34" s="9"/>
       <c r="BR34" s="1"/>
     </row>
     <row r="35" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
+      <c r="D35" s="38">
+        <v>45240</v>
+      </c>
+      <c r="E35" s="38">
+        <v>45242</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
-      <c r="Z35" s="10"/>
-      <c r="AA35" s="10"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="10"/>
-      <c r="AH35" s="10"/>
+      <c r="AG35" s="9"/>
+      <c r="AH35" s="9"/>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
-      <c r="AN35" s="10"/>
-      <c r="AO35" s="10"/>
+      <c r="AN35" s="9"/>
+      <c r="AO35" s="9"/>
       <c r="AP35" s="1"/>
       <c r="AQ35" s="1"/>
       <c r="AR35" s="1"/>
       <c r="AS35" s="1"/>
       <c r="AT35" s="1"/>
-      <c r="AU35" s="10"/>
-      <c r="AV35" s="10"/>
+      <c r="AU35" s="9"/>
+      <c r="AV35" s="9"/>
       <c r="AW35" s="1"/>
       <c r="AX35" s="1"/>
       <c r="AY35" s="1"/>
       <c r="AZ35" s="1"/>
       <c r="BA35" s="1"/>
-      <c r="BB35" s="10"/>
-      <c r="BC35" s="10"/>
+      <c r="BB35" s="9"/>
+      <c r="BC35" s="9"/>
       <c r="BD35" s="1"/>
       <c r="BE35" s="1"/>
       <c r="BF35" s="1"/>
       <c r="BG35" s="1"/>
       <c r="BH35" s="1"/>
-      <c r="BI35" s="10"/>
-      <c r="BJ35" s="10"/>
+      <c r="BI35" s="9"/>
+      <c r="BJ35" s="9"/>
       <c r="BK35" s="1"/>
       <c r="BL35" s="1"/>
       <c r="BM35" s="1"/>
       <c r="BN35" s="1"/>
       <c r="BO35" s="1"/>
-      <c r="BP35" s="10"/>
-      <c r="BQ35" s="10"/>
+      <c r="BP35" s="9"/>
+      <c r="BQ35" s="9"/>
       <c r="BR35" s="1"/>
     </row>
     <row r="36" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="38">
+        <v>45241</v>
+      </c>
+      <c r="E36" s="38">
+        <v>45244</v>
+      </c>
       <c r="F36" s="6"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
       <c r="U36" s="1"/>
       <c r="V36" s="1"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
-      <c r="Z36" s="10"/>
-      <c r="AA36" s="10"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
-      <c r="AG36" s="10"/>
-      <c r="AH36" s="10"/>
+      <c r="AG36" s="9"/>
+      <c r="AH36" s="9"/>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
-      <c r="AN36" s="10"/>
-      <c r="AO36" s="10"/>
+      <c r="AN36" s="9"/>
+      <c r="AO36" s="9"/>
       <c r="AP36" s="1"/>
       <c r="AQ36" s="1"/>
       <c r="AR36" s="1"/>
       <c r="AS36" s="1"/>
       <c r="AT36" s="1"/>
-      <c r="AU36" s="10"/>
-      <c r="AV36" s="10"/>
+      <c r="AU36" s="9"/>
+      <c r="AV36" s="9"/>
       <c r="AW36" s="1"/>
       <c r="AX36" s="1"/>
       <c r="AY36" s="1"/>
       <c r="AZ36" s="1"/>
       <c r="BA36" s="1"/>
-      <c r="BB36" s="10"/>
-      <c r="BC36" s="10"/>
+      <c r="BB36" s="9"/>
+      <c r="BC36" s="9"/>
       <c r="BD36" s="1"/>
       <c r="BE36" s="1"/>
       <c r="BF36" s="1"/>
       <c r="BG36" s="1"/>
       <c r="BH36" s="1"/>
-      <c r="BI36" s="10"/>
-      <c r="BJ36" s="10"/>
+      <c r="BI36" s="9"/>
+      <c r="BJ36" s="9"/>
       <c r="BK36" s="1"/>
       <c r="BL36" s="1"/>
       <c r="BM36" s="1"/>
       <c r="BN36" s="1"/>
       <c r="BO36" s="1"/>
-      <c r="BP36" s="10"/>
-      <c r="BQ36" s="10"/>
+      <c r="BP36" s="9"/>
+      <c r="BQ36" s="9"/>
       <c r="BR36" s="1"/>
     </row>
     <row r="37" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
+      <c r="D37" s="38">
+        <v>45244</v>
+      </c>
+      <c r="E37" s="38">
+        <v>45245</v>
+      </c>
       <c r="F37" s="6"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="10"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
       <c r="W37" s="1"/>
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
-      <c r="Z37" s="10"/>
-      <c r="AA37" s="10"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="10"/>
-      <c r="AH37" s="10"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9"/>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
-      <c r="AN37" s="10"/>
-      <c r="AO37" s="10"/>
+      <c r="AN37" s="9"/>
+      <c r="AO37" s="9"/>
       <c r="AP37" s="1"/>
       <c r="AQ37" s="1"/>
       <c r="AR37" s="1"/>
       <c r="AS37" s="1"/>
       <c r="AT37" s="1"/>
-      <c r="AU37" s="10"/>
-      <c r="AV37" s="10"/>
+      <c r="AU37" s="9"/>
+      <c r="AV37" s="9"/>
       <c r="AW37" s="1"/>
       <c r="AX37" s="1"/>
       <c r="AY37" s="1"/>
       <c r="AZ37" s="1"/>
       <c r="BA37" s="1"/>
-      <c r="BB37" s="10"/>
-      <c r="BC37" s="10"/>
+      <c r="BB37" s="9"/>
+      <c r="BC37" s="9"/>
       <c r="BD37" s="1"/>
       <c r="BE37" s="1"/>
       <c r="BF37" s="1"/>
       <c r="BG37" s="1"/>
       <c r="BH37" s="1"/>
-      <c r="BI37" s="10"/>
-      <c r="BJ37" s="10"/>
+      <c r="BI37" s="9"/>
+      <c r="BJ37" s="9"/>
       <c r="BK37" s="1"/>
       <c r="BL37" s="1"/>
       <c r="BM37" s="1"/>
       <c r="BN37" s="1"/>
       <c r="BO37" s="1"/>
-      <c r="BP37" s="10"/>
-      <c r="BQ37" s="10"/>
+      <c r="BP37" s="9"/>
+      <c r="BQ37" s="9"/>
       <c r="BR37" s="1"/>
     </row>
     <row r="38" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
-      <c r="B38" s="23" t="s">
+      <c r="B38" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24">
+      <c r="C38" s="20"/>
+      <c r="D38" s="39">
+        <v>45246</v>
+      </c>
+      <c r="E38" s="39">
         <v>45266</v>
       </c>
       <c r="F38" s="6"/>
@@ -3703,900 +3835,944 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1"/>
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10"/>
+      <c r="Z38" s="9"/>
+      <c r="AA38" s="9"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
-      <c r="AG38" s="10"/>
-      <c r="AH38" s="10"/>
+      <c r="AG38" s="9"/>
+      <c r="AH38" s="9"/>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
-      <c r="AN38" s="10"/>
-      <c r="AO38" s="10"/>
+      <c r="AN38" s="9"/>
+      <c r="AO38" s="9"/>
       <c r="AP38" s="1"/>
       <c r="AQ38" s="1"/>
       <c r="AR38" s="1"/>
       <c r="AS38" s="1"/>
       <c r="AT38" s="1"/>
-      <c r="AU38" s="10"/>
-      <c r="AV38" s="10"/>
+      <c r="AU38" s="9"/>
+      <c r="AV38" s="9"/>
       <c r="AW38" s="1"/>
       <c r="AX38" s="1"/>
       <c r="AY38" s="1"/>
       <c r="AZ38" s="1"/>
       <c r="BA38" s="1"/>
-      <c r="BB38" s="10"/>
-      <c r="BC38" s="10"/>
+      <c r="BB38" s="9"/>
+      <c r="BC38" s="9"/>
       <c r="BD38" s="1"/>
       <c r="BE38" s="1"/>
       <c r="BF38" s="1"/>
       <c r="BG38" s="1"/>
       <c r="BH38" s="1"/>
-      <c r="BI38" s="10"/>
-      <c r="BJ38" s="10"/>
+      <c r="BI38" s="9"/>
+      <c r="BJ38" s="9"/>
       <c r="BK38" s="1"/>
       <c r="BL38" s="1"/>
       <c r="BM38" s="1"/>
       <c r="BN38" s="1"/>
       <c r="BO38" s="1"/>
-      <c r="BP38" s="10"/>
-      <c r="BQ38" s="10"/>
+      <c r="BP38" s="9"/>
+      <c r="BQ38" s="9"/>
       <c r="BR38" s="1"/>
     </row>
     <row r="39" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
+      <c r="D39" s="40">
+        <v>45246</v>
+      </c>
+      <c r="E39" s="40">
+        <v>45250</v>
+      </c>
       <c r="F39" s="6"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="R39" s="1"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="1"/>
       <c r="Y39" s="1"/>
-      <c r="Z39" s="10"/>
-      <c r="AA39" s="10"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
-      <c r="AG39" s="10"/>
-      <c r="AH39" s="10"/>
+      <c r="AG39" s="9"/>
+      <c r="AH39" s="9"/>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
-      <c r="AN39" s="10"/>
-      <c r="AO39" s="10"/>
+      <c r="AN39" s="9"/>
+      <c r="AO39" s="9"/>
       <c r="AP39" s="1"/>
       <c r="AQ39" s="1"/>
       <c r="AR39" s="1"/>
       <c r="AS39" s="1"/>
       <c r="AT39" s="1"/>
-      <c r="AU39" s="10"/>
-      <c r="AV39" s="10"/>
+      <c r="AU39" s="9"/>
+      <c r="AV39" s="9"/>
       <c r="AW39" s="1"/>
       <c r="AX39" s="1"/>
       <c r="AY39" s="1"/>
       <c r="AZ39" s="1"/>
       <c r="BA39" s="1"/>
-      <c r="BB39" s="10"/>
-      <c r="BC39" s="10"/>
+      <c r="BB39" s="9"/>
+      <c r="BC39" s="9"/>
       <c r="BD39" s="1"/>
       <c r="BE39" s="1"/>
       <c r="BF39" s="1"/>
       <c r="BG39" s="1"/>
       <c r="BH39" s="1"/>
-      <c r="BI39" s="10"/>
-      <c r="BJ39" s="10"/>
+      <c r="BI39" s="9"/>
+      <c r="BJ39" s="9"/>
       <c r="BK39" s="1"/>
       <c r="BL39" s="1"/>
       <c r="BM39" s="1"/>
       <c r="BN39" s="1"/>
       <c r="BO39" s="1"/>
-      <c r="BP39" s="10"/>
-      <c r="BQ39" s="10"/>
+      <c r="BP39" s="9"/>
+      <c r="BQ39" s="9"/>
       <c r="BR39" s="1"/>
     </row>
     <row r="40" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="D40" s="40">
+        <v>45246</v>
+      </c>
+      <c r="E40" s="40">
+        <v>45251</v>
+      </c>
       <c r="F40" s="6"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="1"/>
       <c r="Y40" s="1"/>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="10"/>
+      <c r="Z40" s="9"/>
+      <c r="AA40" s="9"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AG40" s="10"/>
-      <c r="AH40" s="10"/>
+      <c r="AG40" s="9"/>
+      <c r="AH40" s="9"/>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
-      <c r="AN40" s="10"/>
-      <c r="AO40" s="10"/>
+      <c r="AN40" s="9"/>
+      <c r="AO40" s="9"/>
       <c r="AP40" s="1"/>
       <c r="AQ40" s="1"/>
       <c r="AR40" s="1"/>
       <c r="AS40" s="1"/>
       <c r="AT40" s="1"/>
-      <c r="AU40" s="10"/>
-      <c r="AV40" s="10"/>
+      <c r="AU40" s="9"/>
+      <c r="AV40" s="9"/>
       <c r="AW40" s="1"/>
       <c r="AX40" s="1"/>
       <c r="AY40" s="1"/>
       <c r="AZ40" s="1"/>
       <c r="BA40" s="1"/>
-      <c r="BB40" s="10"/>
-      <c r="BC40" s="10"/>
+      <c r="BB40" s="9"/>
+      <c r="BC40" s="9"/>
       <c r="BD40" s="1"/>
       <c r="BE40" s="1"/>
       <c r="BF40" s="1"/>
       <c r="BG40" s="1"/>
       <c r="BH40" s="1"/>
-      <c r="BI40" s="10"/>
-      <c r="BJ40" s="10"/>
+      <c r="BI40" s="9"/>
+      <c r="BJ40" s="9"/>
       <c r="BK40" s="1"/>
       <c r="BL40" s="1"/>
       <c r="BM40" s="1"/>
       <c r="BN40" s="1"/>
       <c r="BO40" s="1"/>
-      <c r="BP40" s="10"/>
-      <c r="BQ40" s="10"/>
+      <c r="BP40" s="9"/>
+      <c r="BQ40" s="9"/>
       <c r="BR40" s="1"/>
     </row>
     <row r="41" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
-      <c r="B41" s="22" t="s">
+      <c r="B41" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="40">
+        <v>45250</v>
+      </c>
+      <c r="E41" s="40">
+        <v>45254</v>
+      </c>
       <c r="F41" s="6"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
       <c r="Y41" s="1"/>
-      <c r="Z41" s="10"/>
-      <c r="AA41" s="10"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AG41" s="10"/>
-      <c r="AH41" s="10"/>
+      <c r="AG41" s="9"/>
+      <c r="AH41" s="9"/>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
-      <c r="AN41" s="10"/>
-      <c r="AO41" s="10"/>
+      <c r="AN41" s="9"/>
+      <c r="AO41" s="9"/>
       <c r="AP41" s="1"/>
       <c r="AQ41" s="1"/>
       <c r="AR41" s="1"/>
       <c r="AS41" s="1"/>
       <c r="AT41" s="1"/>
-      <c r="AU41" s="10"/>
-      <c r="AV41" s="10"/>
+      <c r="AU41" s="9"/>
+      <c r="AV41" s="9"/>
       <c r="AW41" s="1"/>
       <c r="AX41" s="1"/>
       <c r="AY41" s="1"/>
       <c r="AZ41" s="1"/>
       <c r="BA41" s="1"/>
-      <c r="BB41" s="10"/>
-      <c r="BC41" s="10"/>
+      <c r="BB41" s="9"/>
+      <c r="BC41" s="9"/>
       <c r="BD41" s="1"/>
       <c r="BE41" s="1"/>
       <c r="BF41" s="1"/>
       <c r="BG41" s="1"/>
       <c r="BH41" s="1"/>
-      <c r="BI41" s="10"/>
-      <c r="BJ41" s="10"/>
+      <c r="BI41" s="9"/>
+      <c r="BJ41" s="9"/>
       <c r="BK41" s="1"/>
       <c r="BL41" s="1"/>
       <c r="BM41" s="1"/>
       <c r="BN41" s="1"/>
       <c r="BO41" s="1"/>
-      <c r="BP41" s="10"/>
-      <c r="BQ41" s="10"/>
+      <c r="BP41" s="9"/>
+      <c r="BQ41" s="9"/>
       <c r="BR41" s="1"/>
     </row>
     <row r="42" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
+      <c r="D42" s="40">
+        <v>45254</v>
+      </c>
+      <c r="E42" s="40">
+        <v>45256</v>
+      </c>
       <c r="F42" s="6"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
       <c r="W42" s="1"/>
       <c r="X42" s="1"/>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="10"/>
-      <c r="AA42" s="10"/>
+      <c r="Z42" s="9"/>
+      <c r="AA42" s="9"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AG42" s="10"/>
-      <c r="AH42" s="10"/>
+      <c r="AG42" s="9"/>
+      <c r="AH42" s="9"/>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
-      <c r="AN42" s="10"/>
-      <c r="AO42" s="10"/>
+      <c r="AN42" s="9"/>
+      <c r="AO42" s="9"/>
       <c r="AP42" s="1"/>
       <c r="AQ42" s="1"/>
       <c r="AR42" s="1"/>
       <c r="AS42" s="1"/>
       <c r="AT42" s="1"/>
-      <c r="AU42" s="10"/>
-      <c r="AV42" s="10"/>
+      <c r="AU42" s="9"/>
+      <c r="AV42" s="9"/>
       <c r="AW42" s="1"/>
       <c r="AX42" s="1"/>
       <c r="AY42" s="1"/>
       <c r="AZ42" s="1"/>
       <c r="BA42" s="1"/>
-      <c r="BB42" s="10"/>
-      <c r="BC42" s="10"/>
+      <c r="BB42" s="9"/>
+      <c r="BC42" s="9"/>
       <c r="BD42" s="1"/>
       <c r="BE42" s="1"/>
       <c r="BF42" s="1"/>
       <c r="BG42" s="1"/>
       <c r="BH42" s="1"/>
-      <c r="BI42" s="10"/>
-      <c r="BJ42" s="10"/>
+      <c r="BI42" s="9"/>
+      <c r="BJ42" s="9"/>
       <c r="BK42" s="1"/>
       <c r="BL42" s="1"/>
       <c r="BM42" s="1"/>
       <c r="BN42" s="1"/>
       <c r="BO42" s="1"/>
-      <c r="BP42" s="10"/>
-      <c r="BQ42" s="10"/>
+      <c r="BP42" s="9"/>
+      <c r="BQ42" s="9"/>
       <c r="BR42" s="1"/>
     </row>
     <row r="43" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
-      <c r="B43" s="22" t="s">
+      <c r="B43" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
+      <c r="D43" s="40">
+        <v>45254</v>
+      </c>
+      <c r="E43" s="40">
+        <v>45256</v>
+      </c>
       <c r="F43" s="6"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
-      <c r="Z43" s="10"/>
-      <c r="AA43" s="10"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
-      <c r="AG43" s="10"/>
-      <c r="AH43" s="10"/>
+      <c r="AG43" s="9"/>
+      <c r="AH43" s="9"/>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
-      <c r="AN43" s="10"/>
-      <c r="AO43" s="10"/>
+      <c r="AN43" s="9"/>
+      <c r="AO43" s="9"/>
       <c r="AP43" s="1"/>
       <c r="AQ43" s="1"/>
       <c r="AR43" s="1"/>
       <c r="AS43" s="1"/>
       <c r="AT43" s="1"/>
-      <c r="AU43" s="10"/>
-      <c r="AV43" s="10"/>
+      <c r="AU43" s="9"/>
+      <c r="AV43" s="9"/>
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
       <c r="AY43" s="1"/>
       <c r="AZ43" s="1"/>
       <c r="BA43" s="1"/>
-      <c r="BB43" s="10"/>
-      <c r="BC43" s="10"/>
+      <c r="BB43" s="9"/>
+      <c r="BC43" s="9"/>
       <c r="BD43" s="1"/>
       <c r="BE43" s="1"/>
       <c r="BF43" s="1"/>
       <c r="BG43" s="1"/>
       <c r="BH43" s="1"/>
-      <c r="BI43" s="10"/>
-      <c r="BJ43" s="10"/>
+      <c r="BI43" s="9"/>
+      <c r="BJ43" s="9"/>
       <c r="BK43" s="1"/>
       <c r="BL43" s="1"/>
       <c r="BM43" s="1"/>
       <c r="BN43" s="1"/>
       <c r="BO43" s="1"/>
-      <c r="BP43" s="10"/>
-      <c r="BQ43" s="10"/>
+      <c r="BP43" s="9"/>
+      <c r="BQ43" s="9"/>
       <c r="BR43" s="1"/>
     </row>
     <row r="44" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
+      <c r="D44" s="40">
+        <v>45254</v>
+      </c>
+      <c r="E44" s="40">
+        <v>45256</v>
+      </c>
       <c r="F44" s="6"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
-      <c r="S44" s="10"/>
-      <c r="T44" s="10"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="10"/>
-      <c r="AA44" s="10"/>
+      <c r="Z44" s="9"/>
+      <c r="AA44" s="9"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="10"/>
-      <c r="AH44" s="10"/>
+      <c r="AG44" s="9"/>
+      <c r="AH44" s="9"/>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
-      <c r="AN44" s="10"/>
-      <c r="AO44" s="10"/>
+      <c r="AN44" s="9"/>
+      <c r="AO44" s="9"/>
       <c r="AP44" s="1"/>
       <c r="AQ44" s="1"/>
       <c r="AR44" s="1"/>
       <c r="AS44" s="1"/>
       <c r="AT44" s="1"/>
-      <c r="AU44" s="10"/>
-      <c r="AV44" s="10"/>
+      <c r="AU44" s="9"/>
+      <c r="AV44" s="9"/>
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
       <c r="AY44" s="1"/>
       <c r="AZ44" s="1"/>
       <c r="BA44" s="1"/>
-      <c r="BB44" s="10"/>
-      <c r="BC44" s="10"/>
+      <c r="BB44" s="9"/>
+      <c r="BC44" s="9"/>
       <c r="BD44" s="1"/>
       <c r="BE44" s="1"/>
       <c r="BF44" s="1"/>
       <c r="BG44" s="1"/>
       <c r="BH44" s="1"/>
-      <c r="BI44" s="10"/>
-      <c r="BJ44" s="10"/>
+      <c r="BI44" s="9"/>
+      <c r="BJ44" s="9"/>
       <c r="BK44" s="1"/>
       <c r="BL44" s="1"/>
       <c r="BM44" s="1"/>
       <c r="BN44" s="1"/>
       <c r="BO44" s="1"/>
-      <c r="BP44" s="10"/>
-      <c r="BQ44" s="10"/>
+      <c r="BP44" s="9"/>
+      <c r="BQ44" s="9"/>
       <c r="BR44" s="1"/>
     </row>
     <row r="45" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
-      <c r="B45" s="22" t="s">
+      <c r="B45" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
+      <c r="D45" s="40">
+        <v>45255</v>
+      </c>
+      <c r="E45" s="40">
+        <v>45257</v>
+      </c>
       <c r="F45" s="6"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="10"/>
-      <c r="AA45" s="10"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
-      <c r="AG45" s="10"/>
-      <c r="AH45" s="10"/>
+      <c r="AG45" s="9"/>
+      <c r="AH45" s="9"/>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
-      <c r="AN45" s="10"/>
-      <c r="AO45" s="10"/>
+      <c r="AN45" s="9"/>
+      <c r="AO45" s="9"/>
       <c r="AP45" s="1"/>
       <c r="AQ45" s="1"/>
       <c r="AR45" s="1"/>
       <c r="AS45" s="1"/>
       <c r="AT45" s="1"/>
-      <c r="AU45" s="10"/>
-      <c r="AV45" s="10"/>
+      <c r="AU45" s="9"/>
+      <c r="AV45" s="9"/>
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
       <c r="AY45" s="1"/>
       <c r="AZ45" s="1"/>
       <c r="BA45" s="1"/>
-      <c r="BB45" s="10"/>
-      <c r="BC45" s="10"/>
+      <c r="BB45" s="9"/>
+      <c r="BC45" s="9"/>
       <c r="BD45" s="1"/>
       <c r="BE45" s="1"/>
       <c r="BF45" s="1"/>
       <c r="BG45" s="1"/>
       <c r="BH45" s="1"/>
-      <c r="BI45" s="10"/>
-      <c r="BJ45" s="10"/>
+      <c r="BI45" s="9"/>
+      <c r="BJ45" s="9"/>
       <c r="BK45" s="1"/>
       <c r="BL45" s="1"/>
       <c r="BM45" s="1"/>
       <c r="BN45" s="1"/>
       <c r="BO45" s="1"/>
-      <c r="BP45" s="10"/>
-      <c r="BQ45" s="10"/>
+      <c r="BP45" s="9"/>
+      <c r="BQ45" s="9"/>
       <c r="BR45" s="1"/>
     </row>
     <row r="46" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
-      <c r="B46" s="22" t="s">
+      <c r="B46" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
+      <c r="D46" s="40">
+        <v>45257</v>
+      </c>
+      <c r="E46" s="40">
+        <v>45259</v>
+      </c>
       <c r="F46" s="6"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="10"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
       <c r="U46" s="1"/>
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="10"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AG46" s="10"/>
-      <c r="AH46" s="10"/>
+      <c r="AG46" s="9"/>
+      <c r="AH46" s="9"/>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
-      <c r="AN46" s="10"/>
-      <c r="AO46" s="10"/>
+      <c r="AN46" s="9"/>
+      <c r="AO46" s="9"/>
       <c r="AP46" s="1"/>
       <c r="AQ46" s="1"/>
       <c r="AR46" s="1"/>
       <c r="AS46" s="1"/>
       <c r="AT46" s="1"/>
-      <c r="AU46" s="10"/>
-      <c r="AV46" s="10"/>
+      <c r="AU46" s="9"/>
+      <c r="AV46" s="9"/>
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
       <c r="AY46" s="1"/>
       <c r="AZ46" s="1"/>
       <c r="BA46" s="1"/>
-      <c r="BB46" s="10"/>
-      <c r="BC46" s="10"/>
+      <c r="BB46" s="9"/>
+      <c r="BC46" s="9"/>
       <c r="BD46" s="1"/>
       <c r="BE46" s="1"/>
       <c r="BF46" s="1"/>
       <c r="BG46" s="1"/>
       <c r="BH46" s="1"/>
-      <c r="BI46" s="10"/>
-      <c r="BJ46" s="10"/>
+      <c r="BI46" s="9"/>
+      <c r="BJ46" s="9"/>
       <c r="BK46" s="1"/>
       <c r="BL46" s="1"/>
       <c r="BM46" s="1"/>
       <c r="BN46" s="1"/>
       <c r="BO46" s="1"/>
-      <c r="BP46" s="10"/>
-      <c r="BQ46" s="10"/>
+      <c r="BP46" s="9"/>
+      <c r="BQ46" s="9"/>
       <c r="BR46" s="1"/>
     </row>
     <row r="47" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
-      <c r="B47" s="22" t="s">
+      <c r="B47" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
+      <c r="D47" s="40">
+        <v>45257</v>
+      </c>
+      <c r="E47" s="40">
+        <v>45259</v>
+      </c>
       <c r="F47" s="6"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
       <c r="W47" s="1"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="10"/>
-      <c r="AA47" s="10"/>
+      <c r="Z47" s="9"/>
+      <c r="AA47" s="9"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
-      <c r="AG47" s="10"/>
-      <c r="AH47" s="10"/>
+      <c r="AG47" s="9"/>
+      <c r="AH47" s="9"/>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
-      <c r="AN47" s="10"/>
-      <c r="AO47" s="10"/>
+      <c r="AN47" s="9"/>
+      <c r="AO47" s="9"/>
       <c r="AP47" s="1"/>
       <c r="AQ47" s="1"/>
       <c r="AR47" s="1"/>
       <c r="AS47" s="1"/>
       <c r="AT47" s="1"/>
-      <c r="AU47" s="10"/>
-      <c r="AV47" s="10"/>
+      <c r="AU47" s="9"/>
+      <c r="AV47" s="9"/>
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
       <c r="AY47" s="1"/>
       <c r="AZ47" s="1"/>
       <c r="BA47" s="1"/>
-      <c r="BB47" s="10"/>
-      <c r="BC47" s="10"/>
+      <c r="BB47" s="9"/>
+      <c r="BC47" s="9"/>
       <c r="BD47" s="1"/>
       <c r="BE47" s="1"/>
       <c r="BF47" s="1"/>
       <c r="BG47" s="1"/>
       <c r="BH47" s="1"/>
-      <c r="BI47" s="10"/>
-      <c r="BJ47" s="10"/>
+      <c r="BI47" s="9"/>
+      <c r="BJ47" s="9"/>
       <c r="BK47" s="1"/>
       <c r="BL47" s="1"/>
       <c r="BM47" s="1"/>
       <c r="BN47" s="1"/>
       <c r="BO47" s="1"/>
-      <c r="BP47" s="10"/>
-      <c r="BQ47" s="10"/>
+      <c r="BP47" s="9"/>
+      <c r="BQ47" s="9"/>
       <c r="BR47" s="1"/>
     </row>
     <row r="48" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
-      <c r="B48" s="22" t="s">
+      <c r="B48" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
+      <c r="D48" s="40">
+        <v>45260</v>
+      </c>
+      <c r="E48" s="40">
+        <v>45263</v>
+      </c>
       <c r="F48" s="6"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
-      <c r="S48" s="10"/>
-      <c r="T48" s="10"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="10"/>
-      <c r="AA48" s="10"/>
+      <c r="Z48" s="9"/>
+      <c r="AA48" s="9"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
-      <c r="AG48" s="10"/>
-      <c r="AH48" s="10"/>
+      <c r="AG48" s="9"/>
+      <c r="AH48" s="9"/>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
-      <c r="AN48" s="10"/>
-      <c r="AO48" s="10"/>
+      <c r="AN48" s="9"/>
+      <c r="AO48" s="9"/>
       <c r="AP48" s="1"/>
       <c r="AQ48" s="1"/>
       <c r="AR48" s="1"/>
       <c r="AS48" s="1"/>
       <c r="AT48" s="1"/>
-      <c r="AU48" s="10"/>
-      <c r="AV48" s="10"/>
+      <c r="AU48" s="9"/>
+      <c r="AV48" s="9"/>
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
       <c r="AY48" s="1"/>
       <c r="AZ48" s="1"/>
       <c r="BA48" s="1"/>
-      <c r="BB48" s="10"/>
-      <c r="BC48" s="10"/>
+      <c r="BB48" s="9"/>
+      <c r="BC48" s="9"/>
       <c r="BD48" s="1"/>
       <c r="BE48" s="1"/>
       <c r="BF48" s="1"/>
       <c r="BG48" s="1"/>
       <c r="BH48" s="1"/>
-      <c r="BI48" s="10"/>
-      <c r="BJ48" s="10"/>
+      <c r="BI48" s="9"/>
+      <c r="BJ48" s="9"/>
       <c r="BK48" s="1"/>
       <c r="BL48" s="1"/>
       <c r="BM48" s="1"/>
       <c r="BN48" s="1"/>
       <c r="BO48" s="1"/>
-      <c r="BP48" s="10"/>
-      <c r="BQ48" s="10"/>
+      <c r="BP48" s="9"/>
+      <c r="BQ48" s="9"/>
       <c r="BR48" s="1"/>
     </row>
     <row r="49" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
-      <c r="B49" s="22" t="s">
+      <c r="B49" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="22" t="s">
+      <c r="C49" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
+      <c r="D49" s="40">
+        <v>45263</v>
+      </c>
+      <c r="E49" s="40">
+        <v>45265</v>
+      </c>
       <c r="F49" s="6"/>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
       <c r="W49" s="1"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="10"/>
-      <c r="AA49" s="10"/>
+      <c r="Z49" s="9"/>
+      <c r="AA49" s="9"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AG49" s="10"/>
-      <c r="AH49" s="10"/>
+      <c r="AG49" s="9"/>
+      <c r="AH49" s="9"/>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
-      <c r="AN49" s="10"/>
-      <c r="AO49" s="10"/>
+      <c r="AN49" s="9"/>
+      <c r="AO49" s="9"/>
       <c r="AP49" s="1"/>
       <c r="AQ49" s="1"/>
       <c r="AR49" s="1"/>
       <c r="AS49" s="1"/>
       <c r="AT49" s="1"/>
-      <c r="AU49" s="10"/>
-      <c r="AV49" s="10"/>
+      <c r="AU49" s="9"/>
+      <c r="AV49" s="9"/>
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
       <c r="AY49" s="1"/>
       <c r="AZ49" s="1"/>
       <c r="BA49" s="1"/>
-      <c r="BB49" s="10"/>
-      <c r="BC49" s="10"/>
+      <c r="BB49" s="9"/>
+      <c r="BC49" s="9"/>
       <c r="BD49" s="1"/>
       <c r="BE49" s="1"/>
       <c r="BF49" s="1"/>
       <c r="BG49" s="1"/>
       <c r="BH49" s="1"/>
-      <c r="BI49" s="10"/>
-      <c r="BJ49" s="10"/>
+      <c r="BI49" s="9"/>
+      <c r="BJ49" s="9"/>
       <c r="BK49" s="1"/>
       <c r="BL49" s="1"/>
       <c r="BM49" s="1"/>
       <c r="BN49" s="1"/>
       <c r="BO49" s="1"/>
-      <c r="BP49" s="10"/>
-      <c r="BQ49" s="10"/>
+      <c r="BP49" s="9"/>
+      <c r="BQ49" s="9"/>
       <c r="BR49" s="1"/>
     </row>
     <row r="50" spans="1:70" ht="12.75" x14ac:dyDescent="0.2">
@@ -4746,11 +4922,11 @@
     <row r="52" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-      <c r="C52" s="25" t="s">
+      <c r="C52" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D52" s="25"/>
-      <c r="E52" s="26"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="22"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -4818,91 +4994,91 @@
       <c r="BR52" s="1"/>
     </row>
     <row r="53" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="26"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="27" t="s">
+      <c r="A53" s="22"/>
+      <c r="B53" s="22"/>
+      <c r="C53" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="26"/>
-      <c r="O53" s="26"/>
-      <c r="P53" s="26"/>
-      <c r="Q53" s="26"/>
-      <c r="R53" s="26"/>
-      <c r="S53" s="26"/>
-      <c r="T53" s="26"/>
-      <c r="U53" s="26"/>
-      <c r="V53" s="26"/>
-      <c r="W53" s="26"/>
-      <c r="X53" s="26"/>
-      <c r="Y53" s="26"/>
-      <c r="Z53" s="26"/>
-      <c r="AA53" s="26"/>
-      <c r="AB53" s="26"/>
-      <c r="AC53" s="28"/>
-      <c r="AD53" s="26"/>
-      <c r="AE53" s="26"/>
-      <c r="AF53" s="26"/>
-      <c r="AG53" s="26"/>
-      <c r="AH53" s="26"/>
-      <c r="AI53" s="26"/>
-      <c r="AJ53" s="26"/>
-      <c r="AK53" s="26"/>
-      <c r="AL53" s="26"/>
-      <c r="AM53" s="26"/>
-      <c r="AN53" s="26"/>
-      <c r="AO53" s="26"/>
-      <c r="AP53" s="26"/>
-      <c r="AQ53" s="26"/>
-      <c r="AR53" s="26"/>
-      <c r="AS53" s="26"/>
-      <c r="AT53" s="26"/>
-      <c r="AU53" s="26"/>
-      <c r="AV53" s="26"/>
-      <c r="AW53" s="26"/>
-      <c r="AX53" s="26"/>
-      <c r="AY53" s="26"/>
-      <c r="AZ53" s="26"/>
-      <c r="BA53" s="26"/>
-      <c r="BB53" s="26"/>
-      <c r="BC53" s="26"/>
-      <c r="BD53" s="26"/>
-      <c r="BE53" s="26"/>
-      <c r="BF53" s="26"/>
-      <c r="BG53" s="26"/>
-      <c r="BH53" s="26"/>
-      <c r="BI53" s="26"/>
-      <c r="BJ53" s="26"/>
-      <c r="BK53" s="26"/>
-      <c r="BL53" s="26"/>
-      <c r="BM53" s="26"/>
-      <c r="BN53" s="26"/>
-      <c r="BO53" s="26"/>
-      <c r="BP53" s="26"/>
-      <c r="BQ53" s="26"/>
-      <c r="BR53" s="26"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="22"/>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="22"/>
+      <c r="W53" s="22"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="22"/>
+      <c r="Z53" s="22"/>
+      <c r="AA53" s="22"/>
+      <c r="AB53" s="22"/>
+      <c r="AC53" s="24"/>
+      <c r="AD53" s="22"/>
+      <c r="AE53" s="22"/>
+      <c r="AF53" s="22"/>
+      <c r="AG53" s="22"/>
+      <c r="AH53" s="22"/>
+      <c r="AI53" s="22"/>
+      <c r="AJ53" s="22"/>
+      <c r="AK53" s="22"/>
+      <c r="AL53" s="22"/>
+      <c r="AM53" s="22"/>
+      <c r="AN53" s="22"/>
+      <c r="AO53" s="22"/>
+      <c r="AP53" s="22"/>
+      <c r="AQ53" s="22"/>
+      <c r="AR53" s="22"/>
+      <c r="AS53" s="22"/>
+      <c r="AT53" s="22"/>
+      <c r="AU53" s="22"/>
+      <c r="AV53" s="22"/>
+      <c r="AW53" s="22"/>
+      <c r="AX53" s="22"/>
+      <c r="AY53" s="22"/>
+      <c r="AZ53" s="22"/>
+      <c r="BA53" s="22"/>
+      <c r="BB53" s="22"/>
+      <c r="BC53" s="22"/>
+      <c r="BD53" s="22"/>
+      <c r="BE53" s="22"/>
+      <c r="BF53" s="22"/>
+      <c r="BG53" s="22"/>
+      <c r="BH53" s="22"/>
+      <c r="BI53" s="22"/>
+      <c r="BJ53" s="22"/>
+      <c r="BK53" s="22"/>
+      <c r="BL53" s="22"/>
+      <c r="BM53" s="22"/>
+      <c r="BN53" s="22"/>
+      <c r="BO53" s="22"/>
+      <c r="BP53" s="22"/>
+      <c r="BQ53" s="22"/>
+      <c r="BR53" s="22"/>
     </row>
     <row r="54" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="29" t="s">
+      <c r="D54" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E54" s="26"/>
+      <c r="E54" s="22"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -4972,13 +5148,13 @@
     <row r="55" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-      <c r="C55" s="30" t="s">
+      <c r="C55" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="E55" s="26"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -5048,13 +5224,13 @@
     <row r="56" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="31" t="s">
+      <c r="C56" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D56" s="31" t="s">
+      <c r="D56" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E56" s="26"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -5124,13 +5300,13 @@
     <row r="57" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-      <c r="C57" s="32" t="s">
+      <c r="C57" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="D57" s="32" t="s">
+      <c r="D57" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="E57" s="26"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -5200,13 +5376,13 @@
     <row r="58" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D58" s="33" t="s">
+      <c r="D58" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="E58" s="26"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -5276,13 +5452,13 @@
     <row r="59" spans="1:70" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-      <c r="C59" s="34" t="s">
+      <c r="C59" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="E59" s="26"/>
+      <c r="E59" s="22"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
